--- a/results/02-2026/beta/inputs-02-2026.xlsx
+++ b/results/02-2026/beta/inputs-02-2026.xlsx
@@ -845,10 +845,10 @@
     <t xml:space="preserve">2025 Q4</t>
   </si>
   <si>
-    <t xml:space="preserve">projection</t>
+    <t xml:space="preserve">2026 Q1</t>
   </si>
   <si>
-    <t xml:space="preserve">2026 Q1</t>
+    <t xml:space="preserve">projection</t>
   </si>
   <si>
     <t xml:space="preserve">2026 Q2</t>
@@ -1463,7 +1463,7 @@
         <v>0.0110573955976137</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0081228797587638</v>
+        <v>0.00877441803294188</v>
       </c>
       <c r="J2" t="n">
         <v>1051.2</v>
@@ -1621,7 +1621,7 @@
         <v>0.0110573955976137</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0081228797587638</v>
+        <v>0.00877441803294188</v>
       </c>
       <c r="J3" t="n">
         <v>1067.4</v>
@@ -1779,7 +1779,7 @@
         <v>0.0097665191515337</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00785178815127785</v>
+        <v>0.0084356547005342</v>
       </c>
       <c r="J4" t="n">
         <v>1086.1</v>
@@ -1937,7 +1937,7 @@
         <v>0.0129464510604</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00775351968985905</v>
+        <v>0.00814202063388803</v>
       </c>
       <c r="J5" t="n">
         <v>1088.6</v>
@@ -2095,7 +2095,7 @@
         <v>0.0094987069822956</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00795155441845075</v>
+        <v>0.00800250769826483</v>
       </c>
       <c r="J6" t="n">
         <v>1135.2</v>
@@ -2253,7 +2253,7 @@
         <v>0.0113798709296025</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00840013878490176</v>
+        <v>0.00799385369601402</v>
       </c>
       <c r="J7" t="n">
         <v>1156.3</v>
@@ -2411,7 +2411,7 @@
         <v>0.00983925962006804</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00858369098712441</v>
+        <v>0.00798490127758411</v>
       </c>
       <c r="J8" t="n">
         <v>1177.7</v>
@@ -2569,7 +2569,7 @@
         <v>0.00617403048427545</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0085645030972259</v>
+        <v>0.0079576551922802</v>
       </c>
       <c r="J9" t="n">
         <v>1190.3</v>
@@ -2727,7 +2727,7 @@
         <v>0.0105465004793863</v>
       </c>
       <c r="I10" t="n">
-        <v>0.00827814569536423</v>
+        <v>0.0080020005001249</v>
       </c>
       <c r="J10" t="n">
         <v>1230.6</v>
@@ -2885,7 +2885,7 @@
         <v>0.00578747628083498</v>
       </c>
       <c r="I11" t="n">
-        <v>0.00783939827321367</v>
+        <v>0.00804479569054117</v>
       </c>
       <c r="J11" t="n">
         <v>1266.4</v>
@@ -3043,7 +3043,7 @@
         <v>0.0087727572870484</v>
       </c>
       <c r="I12" t="n">
-        <v>0.00758571153273402</v>
+        <v>0.00812122064407261</v>
       </c>
       <c r="J12" t="n">
         <v>1290.6</v>
@@ -3201,7 +3201,7 @@
         <v>0.00813540302973625</v>
       </c>
       <c r="I13" t="n">
-        <v>0.00754598880272628</v>
+        <v>0.00824760244115086</v>
       </c>
       <c r="J13" t="n">
         <v>1328.9</v>
@@ -3359,7 +3359,7 @@
         <v>0.012104628513125</v>
       </c>
       <c r="I14" t="n">
-        <v>0.00771381238351632</v>
+        <v>0.00837037165141896</v>
       </c>
       <c r="J14" t="n">
         <v>1377.5</v>
@@ -3517,7 +3517,7 @@
         <v>0.0191999266828575</v>
       </c>
       <c r="I15" t="n">
-        <v>0.00818563233153524</v>
+        <v>0.00862675150496517</v>
       </c>
       <c r="J15" t="n">
         <v>1413.9</v>
@@ -3675,7 +3675,7 @@
         <v>0.0182087941731857</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0083909432167546</v>
+        <v>0.00865499064784903</v>
       </c>
       <c r="J16" t="n">
         <v>1433.8</v>
@@ -3833,7 +3833,7 @@
         <v>0.0204442089459973</v>
       </c>
       <c r="I17" t="n">
-        <v>0.00860747553354568</v>
+        <v>0.00878302061734026</v>
       </c>
       <c r="J17" t="n">
         <v>1476.3</v>
@@ -3991,7 +3991,7 @@
         <v>0.02977066205106</v>
       </c>
       <c r="I18" t="n">
-        <v>0.00865092354454067</v>
+        <v>0.00882352941176467</v>
       </c>
       <c r="J18" t="n">
         <v>1491.2</v>
@@ -4149,7 +4149,7 @@
         <v>0.0283217077065301</v>
       </c>
       <c r="I19" t="n">
-        <v>0.00864295648718461</v>
+        <v>0.00886231115822955</v>
       </c>
       <c r="J19" t="n">
         <v>1530.1</v>
@@ -4307,7 +4307,7 @@
         <v>0.0269695979078131</v>
       </c>
       <c r="I20" t="n">
-        <v>0.00843757181785354</v>
+        <v>0.00868594322118765</v>
       </c>
       <c r="J20" t="n">
         <v>1560</v>
@@ -4465,7 +4465,7 @@
         <v>0.0254257520292853</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0082693058992056</v>
+        <v>0.00851347831748939</v>
       </c>
       <c r="J21" t="n">
         <v>1599.7</v>
@@ -4623,7 +4623,7 @@
         <v>0.0188196034302122</v>
       </c>
       <c r="I22" t="n">
-        <v>0.00802389409105575</v>
+        <v>0.00823178113146628</v>
       </c>
       <c r="J22" t="n">
         <v>1616.1</v>
@@ -4781,7 +4781,7 @@
         <v>0.0122638634978671</v>
       </c>
       <c r="I23" t="n">
-        <v>0.00786392683825299</v>
+        <v>0.00800448251020569</v>
       </c>
       <c r="J23" t="n">
         <v>1651.9</v>
@@ -4939,7 +4939,7 @@
         <v>0.0187373015275794</v>
       </c>
       <c r="I24" t="n">
-        <v>0.00775489448258337</v>
+        <v>0.00786151036290006</v>
       </c>
       <c r="J24" t="n">
         <v>1709.8</v>
@@ -5097,7 +5097,7 @@
         <v>0.016767617077855</v>
       </c>
       <c r="I25" t="n">
-        <v>0.00766368108994575</v>
+        <v>0.00778443113772442</v>
       </c>
       <c r="J25" t="n">
         <v>1761.8</v>
@@ -5255,7 +5255,7 @@
         <v>0.011006175081729</v>
       </c>
       <c r="I26" t="n">
-        <v>0.00751150198741835</v>
+        <v>0.00766175688776305</v>
       </c>
       <c r="J26" t="n">
         <v>1820.5</v>
@@ -5413,7 +5413,7 @@
         <v>0.00837135774081132</v>
       </c>
       <c r="I27" t="n">
-        <v>0.00747103227610202</v>
+        <v>0.00768108745577556</v>
       </c>
       <c r="J27" t="n">
         <v>1852.3</v>
@@ -5571,7 +5571,7 @@
         <v>0.0151785078030358</v>
       </c>
       <c r="I28" t="n">
-        <v>0.00756980096511106</v>
+        <v>0.00785352407644102</v>
       </c>
       <c r="J28" t="n">
         <v>1886.6</v>
@@ -5729,7 +5729,7 @@
         <v>0.0157939070616313</v>
       </c>
       <c r="I29" t="n">
-        <v>0.00762003855923132</v>
+        <v>0.00788400128344202</v>
       </c>
       <c r="J29" t="n">
         <v>1934.3</v>
@@ -5887,7 +5887,7 @@
         <v>0.018070624006634</v>
       </c>
       <c r="I30" t="n">
-        <v>0.00786612403571652</v>
+        <v>0.00809520200106117</v>
       </c>
       <c r="J30" t="n">
         <v>1988.6</v>
@@ -6045,7 +6045,7 @@
         <v>0.0171050398778212</v>
       </c>
       <c r="I31" t="n">
-        <v>0.00806087087539553</v>
+        <v>0.00822568760432496</v>
       </c>
       <c r="J31" t="n">
         <v>2055.9</v>
@@ -6203,7 +6203,7 @@
         <v>0.0150488838466416</v>
       </c>
       <c r="I32" t="n">
-        <v>0.00817577161647098</v>
+        <v>0.00827789875607787</v>
       </c>
       <c r="J32" t="n">
         <v>2118.5</v>
@@ -6361,7 +6361,7 @@
         <v>0.0142011834319526</v>
       </c>
       <c r="I33" t="n">
-        <v>0.00836150151218651</v>
+        <v>0.0084318279315394</v>
       </c>
       <c r="J33" t="n">
         <v>2164.3</v>
@@ -6519,7 +6519,7 @@
         <v>0.0164008816284196</v>
       </c>
       <c r="I34" t="n">
-        <v>0.00849800047047733</v>
+        <v>0.00858136157603684</v>
       </c>
       <c r="J34" t="n">
         <v>2202.8</v>
@@ -6677,7 +6677,7 @@
         <v>0.020537024044901</v>
       </c>
       <c r="I35" t="n">
-        <v>0.00857217832463486</v>
+        <v>0.00866833439990677</v>
       </c>
       <c r="J35" t="n">
         <v>2331.6</v>
@@ -6835,7 +6835,7 @@
         <v>0.0175614024123492</v>
       </c>
       <c r="I36" t="n">
-        <v>0.0087305946633518</v>
+        <v>0.00883896643211446</v>
       </c>
       <c r="J36" t="n">
         <v>2395.1</v>
@@ -6993,7 +6993,7 @@
         <v>0.0188858862547598</v>
       </c>
       <c r="I37" t="n">
-        <v>0.00882698535522874</v>
+        <v>0.00893303794754519</v>
       </c>
       <c r="J37" t="n">
         <v>2476.9</v>
@@ -7151,7 +7151,7 @@
         <v>0.0188372163115222</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0090622425499276</v>
+        <v>0.00910893894319309</v>
       </c>
       <c r="J38" t="n">
         <v>2526.6</v>
@@ -7309,7 +7309,7 @@
         <v>0.0273340433084841</v>
       </c>
       <c r="I39" t="n">
-        <v>0.00871340090090089</v>
+        <v>0.00870383108952311</v>
       </c>
       <c r="J39" t="n">
         <v>2591.2</v>
@@ -7467,7 +7467,7 @@
         <v>0.0248214697074407</v>
       </c>
       <c r="I40" t="n">
-        <v>0.00814970903864132</v>
+        <v>0.00814162247922834</v>
       </c>
       <c r="J40" t="n">
         <v>2667.6</v>
@@ -7625,7 +7625,7 @@
         <v>0.0241921888170833</v>
       </c>
       <c r="I41" t="n">
-        <v>0.00744708829921237</v>
+        <v>0.00748226069190205</v>
       </c>
       <c r="J41" t="n">
         <v>2723.9</v>
@@ -7783,7 +7783,7 @@
         <v>0.0300128940221118</v>
       </c>
       <c r="I42" t="n">
-        <v>0.00663634739835928</v>
+        <v>0.00667306111263355</v>
       </c>
       <c r="J42" t="n">
         <v>2789.8</v>
@@ -7941,7 +7941,7 @@
         <v>0.0244772939139699</v>
       </c>
       <c r="I43" t="n">
-        <v>0.00567809565407296</v>
+        <v>0.00588019110621096</v>
       </c>
       <c r="J43" t="n">
         <v>2797.4</v>
@@ -8099,7 +8099,7 @@
         <v>0.0233985024958403</v>
       </c>
       <c r="I44" t="n">
-        <v>0.00476384364820848</v>
+        <v>0.00499330166849354</v>
       </c>
       <c r="J44" t="n">
         <v>2856.5</v>
@@ -8257,7 +8257,7 @@
         <v>0.0247434203841075</v>
       </c>
       <c r="I45" t="n">
-        <v>0.00501141413732076</v>
+        <v>0.00518392847525173</v>
       </c>
       <c r="J45" t="n">
         <v>2985.6</v>
@@ -8415,7 +8415,7 @@
         <v>0.025930884029947</v>
       </c>
       <c r="I46" t="n">
-        <v>0.00319883874089411</v>
+        <v>0.00573319223607904</v>
       </c>
       <c r="J46" t="n">
         <v>3124.2</v>
@@ -8573,7 +8573,7 @@
         <v>0.0167697660931763</v>
       </c>
       <c r="I47" t="n">
-        <v>0.0062968917470525</v>
+        <v>0.00611339753066686</v>
       </c>
       <c r="J47" t="n">
         <v>3162.5</v>
@@ -8731,7 +8731,7 @@
         <v>0.0164931793336185</v>
       </c>
       <c r="I48" t="n">
-        <v>0.00669684462787923</v>
+        <v>0.00644691554143506</v>
       </c>
       <c r="J48" t="n">
         <v>3260.6</v>
@@ -8889,7 +8889,7 @@
         <v>0.0153137566632378</v>
       </c>
       <c r="I49" t="n">
-        <v>0.00708872812876082</v>
+        <v>0.00680021571283884</v>
       </c>
       <c r="J49" t="n">
         <v>3280.8</v>
@@ -9047,7 +9047,7 @@
         <v>0.0127109862527921</v>
       </c>
       <c r="I50" t="n">
-        <v>0.00735400333556591</v>
+        <v>0.00704170150501682</v>
       </c>
       <c r="J50" t="n">
         <v>3274.3</v>
@@ -9205,7 +9205,7 @@
         <v>0.00961822688101144</v>
       </c>
       <c r="I51" t="n">
-        <v>0.00753496982101187</v>
+        <v>0.00717408507712469</v>
       </c>
       <c r="J51" t="n">
         <v>3332</v>
@@ -9363,7 +9363,7 @@
         <v>0.0157875771361651</v>
       </c>
       <c r="I52" t="n">
-        <v>0.00768563924075205</v>
+        <v>0.00729043227368731</v>
       </c>
       <c r="J52" t="n">
         <v>3366.3</v>
@@ -9521,7 +9521,7 @@
         <v>0.0110413941422964</v>
       </c>
       <c r="I53" t="n">
-        <v>0.00780678214198582</v>
+        <v>0.00741669011022728</v>
       </c>
       <c r="J53" t="n">
         <v>3402.6</v>
@@ -9679,7 +9679,7 @@
         <v>0.00826736255783866</v>
       </c>
       <c r="I54" t="n">
-        <v>0.00772082712227196</v>
+        <v>0.00732400802213706</v>
       </c>
       <c r="J54" t="n">
         <v>3473.4</v>
@@ -9837,7 +9837,7 @@
         <v>0.0091348036017227</v>
       </c>
       <c r="I55" t="n">
-        <v>0.00785131803527417</v>
+        <v>0.00743456948802268</v>
       </c>
       <c r="J55" t="n">
         <v>3578.8</v>
@@ -9995,7 +9995,7 @@
         <v>0.0131471184102763</v>
       </c>
       <c r="I56" t="n">
-        <v>0.00800341211300104</v>
+        <v>0.00756732416915784</v>
       </c>
       <c r="J56" t="n">
         <v>3689.2</v>
@@ -10153,7 +10153,7 @@
         <v>0.00659462219196727</v>
       </c>
       <c r="I57" t="n">
-        <v>0.00826343430320842</v>
+        <v>0.00782084067830269</v>
       </c>
       <c r="J57" t="n">
         <v>3794.7</v>
@@ -10311,7 +10311,7 @@
         <v>0.0108204066105921</v>
       </c>
       <c r="I58" t="n">
-        <v>0.00851662593497737</v>
+        <v>0.0080927276310605</v>
       </c>
       <c r="J58" t="n">
         <v>3908.1</v>
@@ -10469,7 +10469,7 @@
         <v>0.00968011708132965</v>
       </c>
       <c r="I59" t="n">
-        <v>0.00877515053605515</v>
+        <v>0.00834545032440936</v>
       </c>
       <c r="J59" t="n">
         <v>4009.6</v>
@@ -10627,7 +10627,7 @@
         <v>0.00772368666266332</v>
       </c>
       <c r="I60" t="n">
-        <v>0.00889293296936611</v>
+        <v>0.00848238088313713</v>
       </c>
       <c r="J60" t="n">
         <v>4084.3</v>
@@ -10785,7 +10785,7 @@
         <v>0.00616446800641124</v>
       </c>
       <c r="I61" t="n">
-        <v>0.0089708747204118</v>
+        <v>0.00857925598385068</v>
       </c>
       <c r="J61" t="n">
         <v>4148.6</v>
@@ -10943,7 +10943,7 @@
         <v>0.0118041089735734</v>
       </c>
       <c r="I62" t="n">
-        <v>0.00892686880244087</v>
+        <v>0.00861350044080167</v>
       </c>
       <c r="J62" t="n">
         <v>4230.2</v>
@@ -11101,7 +11101,7 @@
         <v>0.00809381559825617</v>
       </c>
       <c r="I63" t="n">
-        <v>0.00887151075567316</v>
+        <v>0.00859900072052056</v>
       </c>
       <c r="J63" t="n">
         <v>4294.9</v>
@@ -11259,7 +11259,7 @@
         <v>0.00784863349684661</v>
       </c>
       <c r="I64" t="n">
-        <v>0.00877008102664978</v>
+        <v>0.00854911054117036</v>
       </c>
       <c r="J64" t="n">
         <v>4386.8</v>
@@ -11417,7 +11417,7 @@
         <v>0.00697300196674422</v>
       </c>
       <c r="I65" t="n">
-        <v>0.0086357991015984</v>
+        <v>0.00848825462441516</v>
       </c>
       <c r="J65" t="n">
         <v>4444.1</v>
@@ -11575,7 +11575,7 @@
         <v>0.00708254419191912</v>
       </c>
       <c r="I66" t="n">
-        <v>0.00845828969929907</v>
+        <v>0.0083937823834197</v>
       </c>
       <c r="J66" t="n">
         <v>4507.9</v>
@@ -11733,7 +11733,7 @@
         <v>-0.00105784864928393</v>
       </c>
       <c r="I67" t="n">
-        <v>0.00829605623516505</v>
+        <v>0.00830107674214142</v>
       </c>
       <c r="J67" t="n">
         <v>4545.3</v>
@@ -11891,7 +11891,7 @@
         <v>0.00529484439040639</v>
       </c>
       <c r="I68" t="n">
-        <v>0.00818252809561004</v>
+        <v>0.00824406042624504</v>
       </c>
       <c r="J68" t="n">
         <v>4607.7</v>
@@ -12049,7 +12049,7 @@
         <v>0.00604724655209421</v>
       </c>
       <c r="I69" t="n">
-        <v>0.00814979457129361</v>
+        <v>0.00816541995192854</v>
       </c>
       <c r="J69" t="n">
         <v>4657.6</v>
@@ -12207,7 +12207,7 @@
         <v>0.0094623155527116</v>
       </c>
       <c r="I70" t="n">
-        <v>0.008072777480848</v>
+        <v>0.00808814518554835</v>
       </c>
       <c r="J70" t="n">
         <v>4722.2</v>
@@ -12365,7 +12365,7 @@
         <v>0.00966174295537936</v>
       </c>
       <c r="I71" t="n">
-        <v>0.00798603824019972</v>
+        <v>0.00793484146894019</v>
       </c>
       <c r="J71" t="n">
         <v>4806.2</v>
@@ -12523,7 +12523,7 @@
         <v>0.00947416482763863</v>
       </c>
       <c r="I72" t="n">
-        <v>0.0079118085386165</v>
+        <v>0.00778466092867713</v>
       </c>
       <c r="J72" t="n">
         <v>4884.6</v>
@@ -12681,7 +12681,7 @@
         <v>0.00863141231012787</v>
       </c>
       <c r="I73" t="n">
-        <v>0.00790406401530808</v>
+        <v>0.00773540771364845</v>
       </c>
       <c r="J73" t="n">
         <v>5008</v>
@@ -12839,7 +12839,7 @@
         <v>0.00790358744394615</v>
       </c>
       <c r="I74" t="n">
-        <v>0.00783129281052797</v>
+        <v>0.00758966165007657</v>
       </c>
       <c r="J74" t="n">
         <v>5073.4</v>
@@ -12997,7 +12997,7 @@
         <v>0.0110486995532322</v>
       </c>
       <c r="I75" t="n">
-        <v>0.00783465873211231</v>
+        <v>0.00750034823045365</v>
       </c>
       <c r="J75" t="n">
         <v>5190</v>
@@ -13155,7 +13155,7 @@
         <v>0.0123214580392013</v>
       </c>
       <c r="I76" t="n">
-        <v>0.00779499378736892</v>
+        <v>0.0073913367152687</v>
       </c>
       <c r="J76" t="n">
         <v>5282.8</v>
@@ -13313,7 +13313,7 @@
         <v>0.0101066816395283</v>
       </c>
       <c r="I77" t="n">
-        <v>0.00778739053921607</v>
+        <v>0.00731599172332253</v>
       </c>
       <c r="J77" t="n">
         <v>5399.5</v>
@@ -13471,7 +13471,7 @@
         <v>0.0114938406641683</v>
       </c>
       <c r="I78" t="n">
-        <v>0.00774812831987948</v>
+        <v>0.00725237641091203</v>
       </c>
       <c r="J78" t="n">
         <v>5511.3</v>
@@ -13629,7 +13629,7 @@
         <v>0.0134727885126751</v>
       </c>
       <c r="I79" t="n">
-        <v>0.00769893231787666</v>
+        <v>0.00716894359529285</v>
       </c>
       <c r="J79" t="n">
         <v>5612.5</v>
@@ -13787,7 +13787,7 @@
         <v>0.00589470001749159</v>
       </c>
       <c r="I80" t="n">
-        <v>0.00764011161564682</v>
+        <v>0.00709725407549744</v>
       </c>
       <c r="J80" t="n">
         <v>5695.4</v>
@@ -13945,7 +13945,7 @@
         <v>0.00785991270627928</v>
       </c>
       <c r="I81" t="n">
-        <v>0.00755152716608243</v>
+        <v>0.00703698004821263</v>
       </c>
       <c r="J81" t="n">
         <v>5747.2</v>
@@ -14103,7 +14103,7 @@
         <v>0.0144930036750115</v>
       </c>
       <c r="I82" t="n">
-        <v>0.00742393509127792</v>
+        <v>0.00696743437471348</v>
       </c>
       <c r="J82" t="n">
         <v>5872.7</v>
@@ -14261,7 +14261,7 @@
         <v>0.00908178710522289</v>
       </c>
       <c r="I83" t="n">
-        <v>0.0072484194418716</v>
+        <v>0.00687876182287184</v>
       </c>
       <c r="J83" t="n">
         <v>5960</v>
@@ -14419,7 +14419,7 @@
         <v>0.0127079365614415</v>
       </c>
       <c r="I84" t="n">
-        <v>0.00701635149722124</v>
+        <v>0.00674134726478126</v>
       </c>
       <c r="J84" t="n">
         <v>6015.1</v>
@@ -14577,7 +14577,7 @@
         <v>0.0132308153177891</v>
       </c>
       <c r="I85" t="n">
-        <v>0.0067689620263216</v>
+        <v>0.00659641139253142</v>
       </c>
       <c r="J85" t="n">
         <v>6004.7</v>
@@ -14735,7 +14735,7 @@
         <v>0.00525606911730891</v>
       </c>
       <c r="I86" t="n">
-        <v>0.00657557474663806</v>
+        <v>0.00649369962425772</v>
       </c>
       <c r="J86" t="n">
         <v>6035.2</v>
@@ -14893,7 +14893,7 @@
         <v>0.00545733799549031</v>
       </c>
       <c r="I87" t="n">
-        <v>0.00637591451769293</v>
+        <v>0.00637300289592391</v>
       </c>
       <c r="J87" t="n">
         <v>6126.9</v>
@@ -15051,7 +15051,7 @@
         <v>0.00679277171086845</v>
       </c>
       <c r="I88" t="n">
-        <v>0.00622846799151366</v>
+        <v>0.00633264493143715</v>
       </c>
       <c r="J88" t="n">
         <v>6205.9</v>
@@ -15209,7 +15209,7 @@
         <v>0.00726345353003843</v>
       </c>
       <c r="I89" t="n">
-        <v>0.0061899143083739</v>
+        <v>0.00639978213507608</v>
       </c>
       <c r="J89" t="n">
         <v>6264.5</v>
@@ -15367,7 +15367,7 @@
         <v>0.00626562399846153</v>
       </c>
       <c r="I90" t="n">
-        <v>0.00616144721917844</v>
+        <v>0.00645572800896854</v>
       </c>
       <c r="J90" t="n">
         <v>6363.1</v>
@@ -15525,7 +15525,7 @@
         <v>0.00664065610319287</v>
       </c>
       <c r="I91" t="n">
-        <v>0.00620014330069263</v>
+        <v>0.00652954619653934</v>
       </c>
       <c r="J91" t="n">
         <v>6470.8</v>
@@ -15683,7 +15683,7 @@
         <v>0.0063753717648547</v>
       </c>
       <c r="I92" t="n">
-        <v>0.00628536705784066</v>
+        <v>0.00663982751712422</v>
       </c>
       <c r="J92" t="n">
         <v>6566.6</v>
@@ -15841,7 +15841,7 @@
         <v>0.00697948597028986</v>
       </c>
       <c r="I93" t="n">
-        <v>0.00634046006076261</v>
+        <v>0.00670975568149523</v>
       </c>
       <c r="J93" t="n">
         <v>6680.8</v>
@@ -15999,7 +15999,7 @@
         <v>0.005963252626485</v>
       </c>
       <c r="I94" t="n">
-        <v>0.0063942695343997</v>
+        <v>0.00686272663942922</v>
       </c>
       <c r="J94" t="n">
         <v>6729.5</v>
@@ -16157,7 +16157,7 @@
         <v>0.00671932465355907</v>
       </c>
       <c r="I95" t="n">
-        <v>0.00652133407862876</v>
+        <v>0.00692814735169001</v>
       </c>
       <c r="J95" t="n">
         <v>6808.9</v>
@@ -16315,7 +16315,7 @@
         <v>0.00433147331750794</v>
       </c>
       <c r="I96" t="n">
-        <v>0.00659015179563127</v>
+        <v>0.00696404694696184</v>
       </c>
       <c r="J96" t="n">
         <v>6882.1</v>
@@ -16473,7 +16473,7 @@
         <v>0.00577085411710554</v>
       </c>
       <c r="I97" t="n">
-        <v>0.00663895836398409</v>
+        <v>0.0070449809121591</v>
       </c>
       <c r="J97" t="n">
         <v>7013.7</v>
@@ -16631,7 +16631,7 @@
         <v>0.00358608902656754</v>
       </c>
       <c r="I98" t="n">
-        <v>0.00669565376253733</v>
+        <v>0.00711473308305099</v>
       </c>
       <c r="J98" t="n">
         <v>7115.7</v>
@@ -16789,7 +16789,7 @@
         <v>0.00558039108353836</v>
       </c>
       <c r="I99" t="n">
-        <v>0.0067327846688503</v>
+        <v>0.00710993117368397</v>
       </c>
       <c r="J99" t="n">
         <v>7246.9</v>
@@ -16947,7 +16947,7 @@
         <v>0.00716737483555874</v>
       </c>
       <c r="I100" t="n">
-        <v>0.0068319678410802</v>
+        <v>0.00717709828562141</v>
       </c>
       <c r="J100" t="n">
         <v>7331.1</v>
@@ -17105,7 +17105,7 @@
         <v>0.00469920578918126</v>
       </c>
       <c r="I101" t="n">
-        <v>0.00691093664676323</v>
+        <v>0.00723351618801771</v>
       </c>
       <c r="J101" t="n">
         <v>7455.3</v>
@@ -17263,7 +17263,7 @@
         <v>0.00488643156007162</v>
       </c>
       <c r="I102" t="n">
-        <v>0.0069346277971889</v>
+        <v>0.00726166003684225</v>
       </c>
       <c r="J102" t="n">
         <v>7522.3</v>
@@ -17421,7 +17421,7 @@
         <v>0.00582925632370213</v>
       </c>
       <c r="I103" t="n">
-        <v>0.00701930972373055</v>
+        <v>0.00731532773198329</v>
       </c>
       <c r="J103" t="n">
         <v>7581</v>
@@ -17579,7 +17579,7 @@
         <v>0.00408048611008449</v>
       </c>
       <c r="I104" t="n">
-        <v>0.00705806021709021</v>
+        <v>0.00733236854799801</v>
       </c>
       <c r="J104" t="n">
         <v>7683.1</v>
@@ -17737,7 +17737,7 @@
         <v>0.00440256202606193</v>
       </c>
       <c r="I105" t="n">
-        <v>0.00719142600928091</v>
+        <v>0.00745313493134581</v>
       </c>
       <c r="J105" t="n">
         <v>7772.6</v>
@@ -17895,7 +17895,7 @@
         <v>0.00555604421379785</v>
       </c>
       <c r="I106" t="n">
-        <v>0.00729567359640404</v>
+        <v>0.00756220453386569</v>
       </c>
       <c r="J106" t="n">
         <v>7868.5</v>
@@ -18053,7 +18053,7 @@
         <v>0.0066916449200356</v>
       </c>
       <c r="I107" t="n">
-        <v>0.00769765466107164</v>
+        <v>0.00794290713832302</v>
       </c>
       <c r="J107" t="n">
         <v>8032.8</v>
@@ -18211,7 +18211,7 @@
         <v>0.00425766089323987</v>
       </c>
       <c r="I108" t="n">
-        <v>0.00819239350740042</v>
+        <v>0.00839942812404271</v>
       </c>
       <c r="J108" t="n">
         <v>8131.4</v>
@@ -18369,7 +18369,7 @@
         <v>0.00682086926426906</v>
       </c>
       <c r="I109" t="n">
-        <v>0.00865797209176611</v>
+        <v>0.00882737668256039</v>
       </c>
       <c r="J109" t="n">
         <v>8259.8</v>
@@ -18527,7 +18527,7 @@
         <v>0.00441140663716166</v>
       </c>
       <c r="I110" t="n">
-        <v>0.00908611290228034</v>
+        <v>0.00920186379568522</v>
       </c>
       <c r="J110" t="n">
         <v>8362.7</v>
@@ -18685,7 +18685,7 @@
         <v>0.00250973234274965</v>
       </c>
       <c r="I111" t="n">
-        <v>0.00944414015170381</v>
+        <v>0.00947439096161329</v>
       </c>
       <c r="J111" t="n">
         <v>8518.8</v>
@@ -18843,7 +18843,7 @@
         <v>0.00263146665149439</v>
       </c>
       <c r="I112" t="n">
-        <v>0.0098079515932783</v>
+        <v>0.00978782106023779</v>
       </c>
       <c r="J112" t="n">
         <v>8662.8</v>
@@ -19001,7 +19001,7 @@
         <v>0.00314947225059581</v>
       </c>
       <c r="I113" t="n">
-        <v>0.0100709115925393</v>
+        <v>0.0100019516003123</v>
       </c>
       <c r="J113" t="n">
         <v>8765.9</v>
@@ -19159,7 +19159,7 @@
         <v>0.0000707113562439243</v>
       </c>
       <c r="I114" t="n">
-        <v>0.0102687279351312</v>
+        <v>0.010192744311869</v>
       </c>
       <c r="J114" t="n">
         <v>8866.5</v>
@@ -19317,7 +19317,7 @@
         <v>0.00181008272643712</v>
       </c>
       <c r="I115" t="n">
-        <v>0.0104834849210149</v>
+        <v>0.0103847870441214</v>
       </c>
       <c r="J115" t="n">
         <v>8969.7</v>
@@ -19475,7 +19475,7 @@
         <v>0.00309134282850798</v>
       </c>
       <c r="I116" t="n">
-        <v>0.0105642143161686</v>
+        <v>0.010451587458095</v>
       </c>
       <c r="J116" t="n">
         <v>9121.1</v>
@@ -19633,7 +19633,7 @@
         <v>0.00263150488305985</v>
       </c>
       <c r="I117" t="n">
-        <v>0.0106569160572536</v>
+        <v>0.0105620608899297</v>
       </c>
       <c r="J117" t="n">
         <v>9294</v>
@@ -19791,7 +19791,7 @@
         <v>0.00197897514351086</v>
       </c>
       <c r="I118" t="n">
-        <v>0.0107610006493706</v>
+        <v>0.0106756892462903</v>
       </c>
       <c r="J118" t="n">
         <v>9411.7</v>
@@ -19949,7 +19949,7 @@
         <v>0.00568707101835009</v>
       </c>
       <c r="I119" t="n">
-        <v>0.0107764554715943</v>
+        <v>0.0106546413421484</v>
       </c>
       <c r="J119" t="n">
         <v>9526.2</v>
@@ -20107,7 +20107,7 @@
         <v>0.00550169925901156</v>
       </c>
       <c r="I120" t="n">
-        <v>0.010805330024138</v>
+        <v>0.0106255057513858</v>
       </c>
       <c r="J120" t="n">
         <v>9686.6</v>
@@ -20265,7 +20265,7 @@
         <v>0.00606723829840283</v>
       </c>
       <c r="I121" t="n">
-        <v>0.0108545121083954</v>
+        <v>0.0106335214092221</v>
       </c>
       <c r="J121" t="n">
         <v>9900.2</v>
@@ -20423,7 +20423,7 @@
         <v>0.00812347684809089</v>
       </c>
       <c r="I122" t="n">
-        <v>0.0108490391380012</v>
+        <v>0.0105956832401615</v>
       </c>
       <c r="J122" t="n">
         <v>10002.2</v>
@@ -20581,7 +20581,7 @@
         <v>0.00476652235075603</v>
       </c>
       <c r="I123" t="n">
-        <v>0.0104542124542124</v>
+        <v>0.0102647890626144</v>
       </c>
       <c r="J123" t="n">
         <v>10247.7</v>
@@ -20739,7 +20739,7 @@
         <v>0.00644301870378428</v>
       </c>
       <c r="I124" t="n">
-        <v>0.00991829010998568</v>
+        <v>0.00980513028784435</v>
       </c>
       <c r="J124" t="n">
         <v>10318.2</v>
@@ -20897,7 +20897,7 @@
         <v>0.00564544447745874</v>
       </c>
       <c r="I125" t="n">
-        <v>0.00932553214401088</v>
+        <v>0.00930055516055117</v>
       </c>
       <c r="J125" t="n">
         <v>10435.7</v>
@@ -21055,7 +21055,7 @@
         <v>0.00741337630942795</v>
       </c>
       <c r="I126" t="n">
-        <v>0.00874859524588523</v>
+        <v>0.00879502469153381</v>
       </c>
       <c r="J126" t="n">
         <v>10470.2</v>
@@ -21213,7 +21213,7 @@
         <v>0.00467925131978886</v>
       </c>
       <c r="I127" t="n">
-        <v>0.0081862026173285</v>
+        <v>0.00820342808774766</v>
       </c>
       <c r="J127" t="n">
         <v>10599</v>
@@ -21371,7 +21371,7 @@
         <v>0.000504226211801573</v>
       </c>
       <c r="I128" t="n">
-        <v>0.00763716473755993</v>
+        <v>0.00756298405546652</v>
       </c>
       <c r="J128" t="n">
         <v>10598</v>
@@ -21529,7 +21529,7 @@
         <v>0.000411135130833795</v>
       </c>
       <c r="I129" t="n">
-        <v>0.00716283653879524</v>
+        <v>0.00701320704931474</v>
       </c>
       <c r="J129" t="n">
         <v>10660.5</v>
@@ -21687,7 +21687,7 @@
         <v>0.00201505992151874</v>
       </c>
       <c r="I130" t="n">
-        <v>0.00673976114507036</v>
+        <v>0.00652305825242716</v>
       </c>
       <c r="J130" t="n">
         <v>10783.5</v>
@@ -21845,7 +21845,7 @@
         <v>0.00742220575783215</v>
       </c>
       <c r="I131" t="n">
-        <v>0.00644821236660342</v>
+        <v>0.00617250119887647</v>
       </c>
       <c r="J131" t="n">
         <v>10887.5</v>
@@ -22003,7 +22003,7 @@
         <v>0.00517433843325232</v>
       </c>
       <c r="I132" t="n">
-        <v>0.00627087173278751</v>
+        <v>0.00595760905828935</v>
       </c>
       <c r="J132" t="n">
         <v>10984</v>
@@ -22161,7 +22161,7 @@
         <v>0.00466428879394809</v>
       </c>
       <c r="I133" t="n">
-        <v>0.00615744401862783</v>
+        <v>0.00582756893587644</v>
       </c>
       <c r="J133" t="n">
         <v>11061.4</v>
@@ -22319,7 +22319,7 @@
         <v>0.00764669163545562</v>
       </c>
       <c r="I134" t="n">
-        <v>0.00611304429605952</v>
+        <v>0.00582072176949944</v>
       </c>
       <c r="J134" t="n">
         <v>11174.1</v>
@@ -22477,7 +22477,7 @@
         <v>0.00100665943936806</v>
       </c>
       <c r="I135" t="n">
-        <v>0.00612931656117288</v>
+        <v>0.00588070006422603</v>
       </c>
       <c r="J135" t="n">
         <v>11312.8</v>
@@ -22635,7 +22635,7 @@
         <v>0.00658827776488491</v>
       </c>
       <c r="I136" t="n">
-        <v>0.00610524918707278</v>
+        <v>0.00592613284913313</v>
       </c>
       <c r="J136" t="n">
         <v>11566.7</v>
@@ -22793,7 +22793,7 @@
         <v>0.00491847373611876</v>
       </c>
       <c r="I137" t="n">
-        <v>0.00615394762878441</v>
+        <v>0.00606313061186703</v>
       </c>
       <c r="J137" t="n">
         <v>11772.2</v>
@@ -22951,7 +22951,7 @@
         <v>0.00771123035548138</v>
       </c>
       <c r="I138" t="n">
-        <v>0.00623430770340172</v>
+        <v>0.00622375278491583</v>
       </c>
       <c r="J138" t="n">
         <v>11923.4</v>
@@ -23109,7 +23109,7 @@
         <v>0.00672889630922557</v>
       </c>
       <c r="I139" t="n">
-        <v>0.00628037578016083</v>
+        <v>0.00631588572622888</v>
       </c>
       <c r="J139" t="n">
         <v>12112.8</v>
@@ -23267,7 +23267,7 @@
         <v>0.00491243058521995</v>
       </c>
       <c r="I140" t="n">
-        <v>0.00636418961788965</v>
+        <v>0.00643201599241916</v>
       </c>
       <c r="J140" t="n">
         <v>12305.3</v>
@@ -23425,7 +23425,7 @@
         <v>0.00855160342564232</v>
       </c>
       <c r="I141" t="n">
-        <v>0.00638827593749403</v>
+        <v>0.00651343961203121</v>
       </c>
       <c r="J141" t="n">
         <v>12527.2</v>
@@ -23583,7 +23583,7 @@
         <v>0.00581388141665329</v>
       </c>
       <c r="I142" t="n">
-        <v>0.00620069805796697</v>
+        <v>0.00640080987224012</v>
       </c>
       <c r="J142" t="n">
         <v>12767.3</v>
@@ -23741,7 +23741,7 @@
         <v>0.00631023688037669</v>
       </c>
       <c r="I143" t="n">
-        <v>0.00594648166501499</v>
+        <v>0.00623277074990614</v>
       </c>
       <c r="J143" t="n">
         <v>12922.7</v>
@@ -23899,7 +23899,7 @@
         <v>0.010802204531537</v>
       </c>
       <c r="I144" t="n">
-        <v>0.00577870405456604</v>
+        <v>0.00613722066155442</v>
       </c>
       <c r="J144" t="n">
         <v>13142.6</v>
@@ -24057,7 +24057,7 @@
         <v>0.00796054863568063</v>
       </c>
       <c r="I145" t="n">
-        <v>0.00556968384038181</v>
+        <v>0.00601803524040689</v>
       </c>
       <c r="J145" t="n">
         <v>13324.2</v>
@@ -24215,7 +24215,7 @@
         <v>0.0051929942660689</v>
       </c>
       <c r="I146" t="n">
-        <v>0.00533276716913744</v>
+        <v>0.00585701873370881</v>
       </c>
       <c r="J146" t="n">
         <v>13599.2</v>
@@ -24373,7 +24373,7 @@
         <v>0.00877769938173434</v>
       </c>
       <c r="I147" t="n">
-        <v>0.00515540758776623</v>
+        <v>0.00569241094732664</v>
       </c>
       <c r="J147" t="n">
         <v>13753.4</v>
@@ -24531,7 +24531,7 @@
         <v>0.00719577974038299</v>
       </c>
       <c r="I148" t="n">
-        <v>0.00488178661030991</v>
+        <v>0.00541302091057383</v>
       </c>
       <c r="J148" t="n">
         <v>13870.2</v>
@@ -24689,7 +24689,7 @@
         <v>-0.00164779548504035</v>
       </c>
       <c r="I149" t="n">
-        <v>0.00459979337826533</v>
+        <v>0.00514418467438604</v>
       </c>
       <c r="J149" t="n">
         <v>14039.6</v>
@@ -24847,7 +24847,7 @@
         <v>0.00913678055221512</v>
       </c>
       <c r="I150" t="n">
-        <v>0.00469503685022388</v>
+        <v>0.00514231557063805</v>
       </c>
       <c r="J150" t="n">
         <v>14215.7</v>
@@ -25005,7 +25005,7 @@
         <v>0.00849328831617946</v>
       </c>
       <c r="I151" t="n">
-        <v>0.00485587731750869</v>
+        <v>0.00514034041828371</v>
       </c>
       <c r="J151" t="n">
         <v>14402.1</v>
@@ -25163,7 +25163,7 @@
         <v>0.00565312080070424</v>
       </c>
       <c r="I152" t="n">
-        <v>0.00500824602250693</v>
+        <v>0.00513826098008252</v>
       </c>
       <c r="J152" t="n">
         <v>14564.1</v>
@@ -25321,7 +25321,7 @@
         <v>0.0101598857300835</v>
       </c>
       <c r="I153" t="n">
-        <v>0.00500138759848912</v>
+        <v>0.0050397398843931</v>
       </c>
       <c r="J153" t="n">
         <v>14715.1</v>
@@ -25479,7 +25479,7 @@
         <v>0.00814194813784286</v>
       </c>
       <c r="I154" t="n">
-        <v>0.00501251628317423</v>
+        <v>0.00497852225956597</v>
       </c>
       <c r="J154" t="n">
         <v>14706.5</v>
@@ -25637,7 +25637,7 @@
         <v>0.00973893765270106</v>
       </c>
       <c r="I155" t="n">
-        <v>0.0049098663226177</v>
+        <v>0.00474521305768194</v>
       </c>
       <c r="J155" t="n">
         <v>14865.7</v>
@@ -25795,7 +25795,7 @@
         <v>0.0106643963750013</v>
       </c>
       <c r="I156" t="n">
-        <v>0.00474322396576321</v>
+        <v>0.00447360926523621</v>
       </c>
       <c r="J156" t="n">
         <v>14899</v>
@@ -25953,7 +25953,7 @@
         <v>-0.0159608073508385</v>
       </c>
       <c r="I157" t="n">
-        <v>0.00449011464877724</v>
+        <v>0.00414062776878654</v>
       </c>
       <c r="J157" t="n">
         <v>14608.2</v>
@@ -26111,7 +26111,7 @@
         <v>-0.0067582027686105</v>
       </c>
       <c r="I158" t="n">
-        <v>0.00415201682008526</v>
+        <v>0.0037588456402684</v>
       </c>
       <c r="J158" t="n">
         <v>14430.9</v>
@@ -26269,7 +26269,7 @@
         <v>0.0039804493031379</v>
       </c>
       <c r="I159" t="n">
-        <v>0.00388851743674556</v>
+        <v>0.00345175166141187</v>
       </c>
       <c r="J159" t="n">
         <v>14381.2</v>
@@ -26427,7 +26427,7 @@
         <v>0.00689016400849418</v>
       </c>
       <c r="I160" t="n">
-        <v>0.00365144743376278</v>
+        <v>0.00319458963831654</v>
       </c>
       <c r="J160" t="n">
         <v>14448.9</v>
@@ -26585,7 +26585,7 @@
         <v>0.00771802292970758</v>
       </c>
       <c r="I161" t="n">
-        <v>0.00352174166133068</v>
+        <v>0.00307962788314864</v>
       </c>
       <c r="J161" t="n">
         <v>14651.2</v>
@@ -26743,7 +26743,7 @@
         <v>0.00386285205387971</v>
       </c>
       <c r="I162" t="n">
-        <v>0.00352678441950172</v>
+        <v>0.00312240645839013</v>
       </c>
       <c r="J162" t="n">
         <v>14764.6</v>
@@ -26901,7 +26901,7 @@
         <v>0.0015525023010301</v>
       </c>
       <c r="I163" t="n">
-        <v>0.00357797263631277</v>
+        <v>0.0032052580116988</v>
       </c>
       <c r="J163" t="n">
         <v>14980.2</v>
@@ -27059,7 +27059,7 @@
         <v>0.00191547549187865</v>
       </c>
       <c r="I164" t="n">
-        <v>0.00370344771975906</v>
+        <v>0.00338533406384278</v>
       </c>
       <c r="J164" t="n">
         <v>15141.6</v>
@@ -27217,7 +27217,7 @@
         <v>0.00640954801635529</v>
       </c>
       <c r="I165" t="n">
-        <v>0.00378733538002463</v>
+        <v>0.00353484843259655</v>
       </c>
       <c r="J165" t="n">
         <v>15309.5</v>
@@ -27375,7 +27375,7 @@
         <v>0.00840013176677279</v>
       </c>
       <c r="I166" t="n">
-        <v>0.00388738030584546</v>
+        <v>0.00367703912438366</v>
       </c>
       <c r="J166" t="n">
         <v>15351.4</v>
@@ -27533,7 +27533,7 @@
         <v>0.0098328523983231</v>
       </c>
       <c r="I167" t="n">
-        <v>0.00398621907121099</v>
+        <v>0.00377769788688576</v>
       </c>
       <c r="J167" t="n">
         <v>15557.5</v>
@@ -27691,7 +27691,7 @@
         <v>0.00462593543099921</v>
       </c>
       <c r="I168" t="n">
-        <v>0.00408950398457208</v>
+        <v>0.00386581088225757</v>
       </c>
       <c r="J168" t="n">
         <v>15647.7</v>
@@ -27849,7 +27849,7 @@
         <v>0.00330589157104977</v>
       </c>
       <c r="I169" t="n">
-        <v>0.0041632302599619</v>
+        <v>0.00400382827144496</v>
       </c>
       <c r="J169" t="n">
         <v>15842.3</v>
@@ -28007,7 +28007,7 @@
         <v>0.00662209146830706</v>
       </c>
       <c r="I170" t="n">
-        <v>0.00423035164798069</v>
+        <v>0.00413451559045175</v>
       </c>
       <c r="J170" t="n">
         <v>16068.8</v>
@@ -28165,7 +28165,7 @@
         <v>0.00241248113588544</v>
       </c>
       <c r="I171" t="n">
-        <v>0.00433577010335284</v>
+        <v>0.00423545536762515</v>
       </c>
       <c r="J171" t="n">
         <v>16207.1</v>
@@ -28323,7 +28323,7 @@
         <v>0.00290497344175744</v>
       </c>
       <c r="I172" t="n">
-        <v>0.00440071616217375</v>
+        <v>0.00429030904768557</v>
       </c>
       <c r="J172" t="n">
         <v>16319.5</v>
@@ -28481,7 +28481,7 @@
         <v>0.00561340451398062</v>
       </c>
       <c r="I173" t="n">
-        <v>0.00445362565110674</v>
+        <v>0.00434995711309871</v>
       </c>
       <c r="J173" t="n">
         <v>16420.4</v>
@@ -28639,7 +28639,7 @@
         <v>0.00350062023001074</v>
       </c>
       <c r="I174" t="n">
-        <v>0.00454444935869081</v>
+        <v>0.00446421144279996</v>
       </c>
       <c r="J174" t="n">
         <v>16648.2</v>
@@ -28797,7 +28797,7 @@
         <v>0.000513309378895599</v>
       </c>
       <c r="I175" t="n">
-        <v>0.0045844294504187</v>
+        <v>0.00451062232233568</v>
       </c>
       <c r="J175" t="n">
         <v>16728.7</v>
@@ -28955,7 +28955,7 @@
         <v>0.00411483854755623</v>
       </c>
       <c r="I176" t="n">
-        <v>0.00460733557947779</v>
+        <v>0.00453983346615727</v>
       </c>
       <c r="J176" t="n">
         <v>16953.8</v>
@@ -29113,7 +29113,7 @@
         <v>0.00368087924004978</v>
       </c>
       <c r="I177" t="n">
-        <v>0.00465164470814083</v>
+        <v>0.00462327174442345</v>
       </c>
       <c r="J177" t="n">
         <v>17192</v>
@@ -29271,7 +29271,7 @@
         <v>0.00459201695513944</v>
       </c>
       <c r="I178" t="n">
-        <v>0.00469524341987415</v>
+        <v>0.00471091843848037</v>
       </c>
       <c r="J178" t="n">
         <v>17197.7</v>
@@ -29429,7 +29429,7 @@
         <v>0.00447795151816011</v>
       </c>
       <c r="I179" t="n">
-        <v>0.00473813305671689</v>
+        <v>0.00475929770545491</v>
       </c>
       <c r="J179" t="n">
         <v>17518.5</v>
@@ -29587,7 +29587,7 @@
         <v>0.00272833036477271</v>
       </c>
       <c r="I180" t="n">
-        <v>0.00482333267014745</v>
+        <v>0.00486083761781186</v>
       </c>
       <c r="J180" t="n">
         <v>17804.2</v>
@@ -29745,7 +29745,7 @@
         <v>-0.00132451691069269</v>
       </c>
       <c r="I181" t="n">
-        <v>0.00486439625832147</v>
+        <v>0.00493933211639641</v>
       </c>
       <c r="J181" t="n">
         <v>17912.1</v>
@@ -29903,7 +29903,7 @@
         <v>-0.00448259908497406</v>
       </c>
       <c r="I182" t="n">
-        <v>0.00490475404335977</v>
+        <v>0.00501121914734481</v>
       </c>
       <c r="J182" t="n">
         <v>18063.5</v>
@@ -30061,7 +30061,7 @@
         <v>0.00498817503020788</v>
       </c>
       <c r="I183" t="n">
-        <v>0.00493910905256012</v>
+        <v>0.00506065341966222</v>
       </c>
       <c r="J183" t="n">
         <v>18279.8</v>
@@ -30219,7 +30219,7 @@
         <v>0.00259988490628094</v>
       </c>
       <c r="I184" t="n">
-        <v>0.00494647471391652</v>
+        <v>0.00507748452953938</v>
       </c>
       <c r="J184" t="n">
         <v>18401.6</v>
@@ -30377,7 +30377,7 @@
         <v>-0.000768718290370507</v>
       </c>
       <c r="I185" t="n">
-        <v>0.00494311741740483</v>
+        <v>0.00510971951797079</v>
       </c>
       <c r="J185" t="n">
         <v>18435.1</v>
@@ -30535,7 +30535,7 @@
         <v>0.000492358190583575</v>
       </c>
       <c r="I186" t="n">
-        <v>0.00491880319565552</v>
+        <v>0.00514133433856379</v>
       </c>
       <c r="J186" t="n">
         <v>18525.9</v>
@@ -30693,7 +30693,7 @@
         <v>0.0063462445405893</v>
       </c>
       <c r="I187" t="n">
-        <v>0.00491031529939923</v>
+        <v>0.00511503622716591</v>
       </c>
       <c r="J187" t="n">
         <v>18711.7</v>
@@ -30851,7 +30851,7 @@
         <v>0.00345365078394821</v>
       </c>
       <c r="I188" t="n">
-        <v>0.00488115120710231</v>
+        <v>0.00506309434353391</v>
       </c>
       <c r="J188" t="n">
         <v>18892.6</v>
@@ -31009,7 +31009,7 @@
         <v>0.00457886614684866</v>
       </c>
       <c r="I189" t="n">
-        <v>0.00483685892323282</v>
+        <v>0.0050118076538348</v>
       </c>
       <c r="J189" t="n">
         <v>19089.4</v>
@@ -31167,7 +31167,7 @@
         <v>0.00583140469140053</v>
       </c>
       <c r="I190" t="n">
-        <v>0.00481869715947791</v>
+        <v>0.00498681469776407</v>
       </c>
       <c r="J190" t="n">
         <v>19280.1</v>
@@ -31325,7 +31325,7 @@
         <v>0.0020095655319321</v>
       </c>
       <c r="I191" t="n">
-        <v>0.00483635881807332</v>
+        <v>0.00496717478533437</v>
       </c>
       <c r="J191" t="n">
         <v>19438.6</v>
@@ -31483,7 +31483,7 @@
         <v>0.00352974208816326</v>
       </c>
       <c r="I192" t="n">
-        <v>0.00493987452515854</v>
+        <v>0.00497310257595518</v>
       </c>
       <c r="J192" t="n">
         <v>19692.6</v>
@@ -31641,7 +31641,7 @@
         <v>0.00599544346296832</v>
       </c>
       <c r="I193" t="n">
-        <v>0.00503671553660201</v>
+        <v>0.00499903961827353</v>
       </c>
       <c r="J193" t="n">
         <v>20037.1</v>
@@ -31799,7 +31799,7 @@
         <v>0.00699272915093951</v>
       </c>
       <c r="I194" t="n">
-        <v>0.00513199057963387</v>
+        <v>0.00505967499383875</v>
       </c>
       <c r="J194" t="n">
         <v>20328.6</v>
@@ -31957,7 +31957,7 @@
         <v>0.00524758334977315</v>
       </c>
       <c r="I195" t="n">
-        <v>0.0052556640771364</v>
+        <v>0.00512928295126436</v>
       </c>
       <c r="J195" t="n">
         <v>20580.9</v>
@@ -32115,7 +32115,7 @@
         <v>0.0033558364078814</v>
       </c>
       <c r="I196" t="n">
-        <v>0.00528782359343394</v>
+        <v>0.00514791544275073</v>
       </c>
       <c r="J196" t="n">
         <v>20798.7</v>
@@ -32273,7 +32273,7 @@
         <v>0.00379447258786936</v>
       </c>
       <c r="I197" t="n">
-        <v>0.00528967129883684</v>
+        <v>0.00521070671448109</v>
       </c>
       <c r="J197" t="n">
         <v>20917.9</v>
@@ -32431,7 +32431,7 @@
         <v>0.00203620350343914</v>
       </c>
       <c r="I198" t="n">
-        <v>0.00530609635556267</v>
+        <v>0.00529210028382199</v>
       </c>
       <c r="J198" t="n">
         <v>21111.6</v>
@@ -32589,7 +32589,7 @@
         <v>0.00559061166152985</v>
       </c>
       <c r="I199" t="n">
-        <v>0.00528787359976524</v>
+        <v>0.0052887490319482</v>
       </c>
       <c r="J199" t="n">
         <v>21397.9</v>
@@ -32747,7 +32747,7 @@
         <v>0.00240751841896625</v>
       </c>
       <c r="I200" t="n">
-        <v>0.00525032723309216</v>
+        <v>0.0052658010599862</v>
       </c>
       <c r="J200" t="n">
         <v>21717.2</v>
@@ -32905,7 +32905,7 @@
         <v>0.00393537496985763</v>
       </c>
       <c r="I201" t="n">
-        <v>0.00508253061619635</v>
+        <v>0.00509756180369281</v>
       </c>
       <c r="J201" t="n">
         <v>21933.2</v>
@@ -33063,7 +33063,7 @@
         <v>0.0034779935243987</v>
       </c>
       <c r="I202" t="n">
-        <v>0.00497495665575021</v>
+        <v>0.00497519640203081</v>
       </c>
       <c r="J202" t="n">
         <v>21751.2</v>
@@ -33221,7 +33221,7 @@
         <v>-0.0040978505433481</v>
       </c>
       <c r="I203" t="n">
-        <v>0.00494074460998806</v>
+        <v>0.00480171325128809</v>
       </c>
       <c r="J203" t="n">
         <v>19958.3</v>
@@ -33379,7 +33379,7 @@
         <v>0.00786409913764086</v>
       </c>
       <c r="I204" t="n">
-        <v>0.00483538702170661</v>
+        <v>0.00452071356548567</v>
       </c>
       <c r="J204" t="n">
         <v>21704.4</v>
@@ -33537,7 +33537,7 @@
         <v>0.00509371870081554</v>
       </c>
       <c r="I205" t="n">
-        <v>0.00486432103569689</v>
+        <v>0.00457172759924829</v>
       </c>
       <c r="J205" t="n">
         <v>22087.2</v>
@@ -33695,7 +33695,7 @@
         <v>0.011369567899477</v>
       </c>
       <c r="I206" t="n">
-        <v>0.00488327831380508</v>
+        <v>0.00474981767898264</v>
       </c>
       <c r="J206" t="n">
         <v>22680.7</v>
@@ -33853,7 +33853,7 @@
         <v>0.0151735527883867</v>
       </c>
       <c r="I207" t="n">
-        <v>0.00494414339895766</v>
+        <v>0.00496773798245731</v>
       </c>
       <c r="J207" t="n">
         <v>23425.9</v>
@@ -34011,7 +34011,7 @@
         <v>0.013597204762257</v>
       </c>
       <c r="I208" t="n">
-        <v>0.0051489741803028</v>
+        <v>0.00529961589509576</v>
       </c>
       <c r="J208" t="n">
         <v>23982.4</v>
@@ -34169,7 +34169,7 @@
         <v>0.0166795859741917</v>
       </c>
       <c r="I209" t="n">
-        <v>0.00526217838365972</v>
+        <v>0.00553759452865132</v>
       </c>
       <c r="J209" t="n">
         <v>24813.6</v>
@@ -34327,7 +34327,7 @@
         <v>0.0188188439596713</v>
       </c>
       <c r="I210" t="n">
-        <v>0.0053642258436275</v>
+        <v>0.00578546905446786</v>
       </c>
       <c r="J210" t="n">
         <v>25250.3</v>
@@ -34485,7 +34485,7 @@
         <v>0.0182775439770386</v>
       </c>
       <c r="I211" t="n">
-        <v>0.00545990240309346</v>
+        <v>0.00601050801016667</v>
       </c>
       <c r="J211" t="n">
         <v>25861.3</v>
@@ -34643,7 +34643,7 @@
         <v>0.0114821283439106</v>
       </c>
       <c r="I212" t="n">
-        <v>0.00553556220982943</v>
+        <v>0.00622220184327582</v>
       </c>
       <c r="J212" t="n">
         <v>26336.3</v>
@@ -34801,7 +34801,7 @@
         <v>0.0101721573521618</v>
       </c>
       <c r="I213" t="n">
-        <v>0.00561892402613662</v>
+        <v>0.00638422944947981</v>
       </c>
       <c r="J213" t="n">
         <v>26770.5</v>
@@ -34959,7 +34959,7 @@
         <v>0.00957893311670732</v>
       </c>
       <c r="I214" t="n">
-        <v>0.00558300014942326</v>
+        <v>0.00655201767731661</v>
       </c>
       <c r="J214" t="n">
         <v>27216.4</v>
@@ -35117,7 +35117,7 @@
         <v>0.00739263083783137</v>
       </c>
       <c r="I215" t="n">
-        <v>0.00562404877477674</v>
+        <v>0.00667581367102277</v>
       </c>
       <c r="J215" t="n">
         <v>27530.1</v>
@@ -35275,7 +35275,7 @@
         <v>0.00673100923537739</v>
       </c>
       <c r="I216" t="n">
-        <v>0.00566871594180851</v>
+        <v>0.00668963575670634</v>
       </c>
       <c r="J216" t="n">
         <v>28074.8</v>
@@ -35433,7 +35433,7 @@
         <v>0.00452069851816961</v>
       </c>
       <c r="I217" t="n">
-        <v>0.00572135870024981</v>
+        <v>0.00668513290363837</v>
       </c>
       <c r="J217" t="n">
         <v>28424.7</v>
@@ -35591,7 +35591,7 @@
         <v>0.00885261547068583</v>
       </c>
       <c r="I218" t="n">
-        <v>0.00575079023560954</v>
+        <v>0.00664514820400219</v>
       </c>
       <c r="J218" t="n">
         <v>28708.2</v>
@@ -35749,7 +35749,7 @@
         <v>0.006418097894342</v>
       </c>
       <c r="I219" t="n">
-        <v>0.0058015415021504</v>
+        <v>0.00657499923342764</v>
       </c>
       <c r="J219" t="n">
         <v>29147</v>
@@ -35907,7 +35907,7 @@
         <v>0.00422173423332173</v>
       </c>
       <c r="I220" t="n">
-        <v>0.00575057221256969</v>
+        <v>0.00643631141477008</v>
       </c>
       <c r="J220" t="n">
         <v>29511.7</v>
@@ -36065,7 +36065,7 @@
         <v>0.00623739207617202</v>
       </c>
       <c r="I221" t="n">
-        <v>0.00574380039423361</v>
+        <v>0.00625245925740159</v>
       </c>
       <c r="J221" t="n">
         <v>29825.2</v>
@@ -36223,7 +36223,7 @@
         <v>0.0084681202537229</v>
       </c>
       <c r="I222" t="n">
-        <v>0.00562014078474316</v>
+        <v>0.00615344949831331</v>
       </c>
       <c r="J222" t="n">
         <v>30042.1</v>
@@ -36381,7 +36381,7 @@
         <v>0.00528789192026013</v>
       </c>
       <c r="I223" t="n">
-        <v>0.00571780133544419</v>
+        <v>0.00571435892836547</v>
       </c>
       <c r="J223" t="n">
         <v>30485.7</v>
@@ -36539,7 +36539,7 @@
         <v>0.006873694868063</v>
       </c>
       <c r="I224" t="n">
-        <v>0.00573662843673683</v>
+        <v>0.00559271291165042</v>
       </c>
       <c r="J224" t="n">
         <v>31098</v>
@@ -36676,55 +36676,55 @@
         <v>276</v>
       </c>
       <c r="B225" t="s">
-        <v>277</v>
+        <v>53</v>
       </c>
       <c r="C225" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D225" t="n">
-        <v>0.0235414933379692</v>
+        <v>0.036975382986721</v>
       </c>
       <c r="E225" t="n">
-        <v>0.00881274147561828</v>
+        <v>0.00471199081611995</v>
       </c>
       <c r="F225" t="n">
-        <v>0.00881274147561828</v>
+        <v>0.0114539487506429</v>
       </c>
       <c r="G225" t="n">
-        <v>0.00881274147561828</v>
+        <v>0.00601937837051625</v>
       </c>
       <c r="H225" t="n">
-        <v>0.0070632593748059</v>
+        <v>0.00721170842073016</v>
       </c>
       <c r="I225" t="n">
         <v>0.0055320478712173</v>
       </c>
       <c r="J225" t="n">
-        <v>31455.7922391607</v>
+        <v>31490.1</v>
       </c>
       <c r="K225" t="n">
-        <v>21328.971296046</v>
+        <v>21387.3</v>
       </c>
       <c r="L225" t="n">
         <v>0</v>
       </c>
       <c r="M225" t="n">
-        <v>1963.97602864807</v>
+        <v>1972</v>
       </c>
       <c r="N225" t="n">
-        <v>436.280590481267</v>
+        <v>409.7113188</v>
       </c>
       <c r="O225" t="n">
         <v>75.1961428571429</v>
       </c>
       <c r="P225" t="n">
-        <v>3370.16982968662</v>
+        <v>3374.4</v>
       </c>
       <c r="Q225" t="n">
-        <v>5212.81672683151</v>
+        <v>5136.9</v>
       </c>
       <c r="R225" t="n">
-        <v>2545.84671222589</v>
+        <v>2564.4</v>
       </c>
       <c r="S225" t="n">
         <v>457.716813873374</v>
@@ -36736,10 +36736,10 @@
         <v>163.113202913515</v>
       </c>
       <c r="V225" t="n">
-        <v>2377.5591791801</v>
+        <v>2372.439</v>
       </c>
       <c r="W225" t="n">
-        <v>223.324677586102</v>
+        <v>205.5</v>
       </c>
       <c r="X225" t="n">
         <v>0</v>
@@ -36751,10 +36751,10 @@
         <v>0</v>
       </c>
       <c r="AA225" t="n">
-        <v>35.7</v>
+        <v>38.3</v>
       </c>
       <c r="AB225" t="n">
-        <v>128.64</v>
+        <v>97.3</v>
       </c>
       <c r="AC225" t="n">
         <v>-2.15</v>
@@ -36769,19 +36769,19 @@
         <v>-8.28246</v>
       </c>
       <c r="AG225" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="AH225" t="n">
-        <v>1955.32211778154</v>
+        <v>1975.018</v>
       </c>
       <c r="AI225" t="n">
-        <v>372.653717523706</v>
+        <v>372.882</v>
       </c>
       <c r="AJ225" t="n">
-        <v>-2887.39400721978</v>
+        <v>-2878.284</v>
       </c>
       <c r="AK225" t="n">
-        <v>-1476.91760546711</v>
+        <v>-1479.144</v>
       </c>
       <c r="AL225" t="n">
         <v>-175.923893795779</v>
@@ -36790,10 +36790,10 @@
         <v>-69.0204400971171</v>
       </c>
       <c r="AN225" t="n">
-        <v>2131.18946531552</v>
+        <v>2130.037425</v>
       </c>
       <c r="AO225" t="n">
-        <v>187.678052456873</v>
+        <v>183.6675</v>
       </c>
       <c r="AP225" t="n">
         <v>0</v>
@@ -36805,10 +36805,10 @@
         <v>0</v>
       </c>
       <c r="AS225" t="n">
-        <v>33.762</v>
+        <v>34.282</v>
       </c>
       <c r="AT225" t="n">
-        <v>48.740355</v>
+        <v>47.189025</v>
       </c>
       <c r="AU225" t="n">
         <v>0.573855</v>
@@ -36820,27 +36820,27 @@
         <v>-1.64145683</v>
       </c>
       <c r="AX225" t="n">
-        <v>0.28035</v>
+        <v>0.315</v>
       </c>
       <c r="AY225" t="n">
-        <v>1705.78060150085</v>
+        <v>1710.212175</v>
       </c>
       <c r="AZ225" t="n">
-        <v>304.768961442834</v>
+        <v>304.820325</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="s">
+        <v>277</v>
+      </c>
+      <c r="B226" t="s">
         <v>278</v>
       </c>
-      <c r="B226" t="s">
-        <v>277</v>
-      </c>
       <c r="C226" t="n">
         <v>0</v>
       </c>
       <c r="D226" t="n">
-        <v>-0.016194151620221</v>
+        <v>-0.0285004322590822</v>
       </c>
       <c r="E226" t="n">
         <v>0.00825837924065231</v>
@@ -36858,31 +36858,31 @@
         <v>0.00562340411235041</v>
       </c>
       <c r="J226" t="n">
-        <v>31853.1494915769</v>
+        <v>31887.8906364327</v>
       </c>
       <c r="K226" t="n">
-        <v>21559.0579343511</v>
+        <v>21618.0158601848</v>
       </c>
       <c r="L226" t="n">
         <v>0.06</v>
       </c>
       <c r="M226" t="n">
-        <v>2066.43850123648</v>
+        <v>2074.88109070427</v>
       </c>
       <c r="N226" t="n">
-        <v>439.294267404661</v>
+        <v>412.463197887809</v>
       </c>
       <c r="O226" t="n">
         <v>75.1961428571429</v>
       </c>
       <c r="P226" t="n">
-        <v>3402.28886190014</v>
+        <v>3406.55934738558</v>
       </c>
       <c r="Q226" t="n">
-        <v>5173.01761417514</v>
+        <v>5083.4035395912</v>
       </c>
       <c r="R226" t="n">
-        <v>2575.18382480724</v>
+        <v>2587.09562716461</v>
       </c>
       <c r="S226" t="n">
         <v>445.021075130373</v>
@@ -36894,7 +36894,7 @@
         <v>166.425523958362</v>
       </c>
       <c r="V226" t="n">
-        <v>2443.78680181216</v>
+        <v>2450.52030581216</v>
       </c>
       <c r="W226" t="n">
         <v>226.552471112076</v>
@@ -36912,7 +36912,7 @@
         <v>35.7</v>
       </c>
       <c r="AB226" t="n">
-        <v>126.49</v>
+        <v>107.3</v>
       </c>
       <c r="AC226" t="n">
         <v>0</v>
@@ -36930,16 +36930,16 @@
         <v>0</v>
       </c>
       <c r="AH226" t="n">
-        <v>2000.57395645475</v>
+        <v>2013.8753546001</v>
       </c>
       <c r="AI226" t="n">
-        <v>378.384322734311</v>
+        <v>384.007881017631</v>
       </c>
       <c r="AJ226" t="n">
-        <v>-2941.7981209208</v>
+        <v>-2921.93442475094</v>
       </c>
       <c r="AK226" t="n">
-        <v>-1494.99366444398</v>
+        <v>-1498.64947525975</v>
       </c>
       <c r="AL226" t="n">
         <v>-176.784596300125</v>
@@ -36948,10 +36948,10 @@
         <v>-68.7712908957292</v>
       </c>
       <c r="AN226" t="n">
-        <v>2160.66194572326</v>
+        <v>2161.02494380774</v>
       </c>
       <c r="AO226" t="n">
-        <v>192.90985845709</v>
+        <v>188.899306000217</v>
       </c>
       <c r="AP226" t="n">
         <v>0</v>
@@ -36963,10 +36963,10 @@
         <v>0</v>
       </c>
       <c r="AS226" t="n">
-        <v>33.567</v>
+        <v>34.009</v>
       </c>
       <c r="AT226" t="n">
-        <v>49.24449</v>
+        <v>46.9548</v>
       </c>
       <c r="AU226" t="n">
         <v>0.378236</v>
@@ -36978,13 +36978,13 @@
         <v>-3.38712266</v>
       </c>
       <c r="AX226" t="n">
-        <v>0.250425</v>
+        <v>0.28035</v>
       </c>
       <c r="AY226" t="n">
-        <v>1748.36004170317</v>
+        <v>1755.78442978502</v>
       </c>
       <c r="AZ226" t="n">
-        <v>318.700134058054</v>
+        <v>320.016798228967</v>
       </c>
     </row>
     <row r="227">
@@ -36992,7 +36992,7 @@
         <v>279</v>
       </c>
       <c r="B227" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C227" t="n">
         <v>0</v>
@@ -37016,31 +37016,31 @@
         <v>0.00525368446989161</v>
       </c>
       <c r="J227" t="n">
-        <v>32229.3183739501</v>
+        <v>32264.4697933892</v>
       </c>
       <c r="K227" t="n">
-        <v>21829.0943414481</v>
+        <v>21888.7907404799</v>
       </c>
       <c r="L227" t="n">
         <v>0.06</v>
       </c>
       <c r="M227" t="n">
-        <v>2059.60088994878</v>
+        <v>2068.01554384286</v>
       </c>
       <c r="N227" t="n">
-        <v>439.534639311989</v>
+        <v>412.439192359044</v>
       </c>
       <c r="O227" t="n">
         <v>75.1961428571429</v>
       </c>
       <c r="P227" t="n">
-        <v>3434.76360251492</v>
+        <v>3439.07484965055</v>
       </c>
       <c r="Q227" t="n">
-        <v>5212.84630338752</v>
+        <v>5104.38252372255</v>
       </c>
       <c r="R227" t="n">
-        <v>2608.17814335716</v>
+        <v>2620.25184393131</v>
       </c>
       <c r="S227" t="n">
         <v>432.67747940975</v>
@@ -37052,7 +37052,7 @@
         <v>166.941911087545</v>
       </c>
       <c r="V227" t="n">
-        <v>2465.17262342837</v>
+        <v>2471.90612742837</v>
       </c>
       <c r="W227" t="n">
         <v>229.826917122492</v>
@@ -37070,7 +37070,7 @@
         <v>35.7</v>
       </c>
       <c r="AB227" t="n">
-        <v>126.49</v>
+        <v>107.3</v>
       </c>
       <c r="AC227" t="n">
         <v>0</v>
@@ -37088,16 +37088,16 @@
         <v>0</v>
       </c>
       <c r="AH227" t="n">
-        <v>2051.36481041804</v>
+        <v>2064.5130048501</v>
       </c>
       <c r="AI227" t="n">
-        <v>384.936785140479</v>
+        <v>389.669595040581</v>
       </c>
       <c r="AJ227" t="n">
-        <v>-2987.17467371741</v>
+        <v>-2958.85032759765</v>
       </c>
       <c r="AK227" t="n">
-        <v>-1513.40823891328</v>
+        <v>-1517.39969653151</v>
       </c>
       <c r="AL227" t="n">
         <v>-177.357178947116</v>
@@ -37106,10 +37106,10 @@
         <v>-68.6626879319807</v>
       </c>
       <c r="AN227" t="n">
-        <v>2173.14373599464</v>
+        <v>2175.02177247912</v>
       </c>
       <c r="AO227" t="n">
-        <v>198.833414809651</v>
+        <v>194.822862352778</v>
       </c>
       <c r="AP227" t="n">
         <v>0</v>
@@ -37121,10 +37121,10 @@
         <v>0</v>
       </c>
       <c r="AS227" t="n">
-        <v>33.316</v>
+        <v>33.732</v>
       </c>
       <c r="AT227" t="n">
-        <v>49.9326975</v>
+        <v>46.89315</v>
       </c>
       <c r="AU227" t="n">
         <v>0.211344</v>
@@ -37136,13 +37136,13 @@
         <v>-5.02566645</v>
       </c>
       <c r="AX227" t="n">
-        <v>0.222075</v>
+        <v>0.250425</v>
       </c>
       <c r="AY227" t="n">
-        <v>1787.44362404723</v>
+        <v>1797.82635587629</v>
       </c>
       <c r="AZ227" t="n">
-        <v>333.504410714662</v>
+        <v>335.885957113098</v>
       </c>
     </row>
     <row r="228">
@@ -37150,7 +37150,7 @@
         <v>280</v>
       </c>
       <c r="B228" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C228" t="n">
         <v>0</v>
@@ -37174,31 +37174,31 @@
         <v>0.00537994009364007</v>
       </c>
       <c r="J228" t="n">
-        <v>32604.282230539</v>
+        <v>32639.8426102807</v>
       </c>
       <c r="K228" t="n">
-        <v>22076.4024339693</v>
+        <v>22136.7751506872</v>
       </c>
       <c r="L228" t="n">
         <v>0.06</v>
       </c>
       <c r="M228" t="n">
-        <v>2075.70755692998</v>
+        <v>2084.18801581993</v>
       </c>
       <c r="N228" t="n">
-        <v>443.6079988</v>
+        <v>416.245569392601</v>
       </c>
       <c r="O228" t="n">
         <v>75.1961428571429</v>
       </c>
       <c r="P228" t="n">
-        <v>3467.9905480353</v>
+        <v>3472.3435009738</v>
       </c>
       <c r="Q228" t="n">
-        <v>5253.06108665003</v>
+        <v>5143.51718245347</v>
       </c>
       <c r="R228" t="n">
-        <v>2637.90994797988</v>
+        <v>2650.12168418405</v>
       </c>
       <c r="S228" t="n">
         <v>420.676259283967</v>
@@ -37210,7 +37210,7 @@
         <v>167.560645215304</v>
       </c>
       <c r="V228" t="n">
-        <v>2488.398292</v>
+        <v>2495.131796</v>
       </c>
       <c r="W228" t="n">
         <v>233.148689902827</v>
@@ -37228,7 +37228,7 @@
         <v>35.7</v>
       </c>
       <c r="AB228" t="n">
-        <v>126.49</v>
+        <v>107.3</v>
       </c>
       <c r="AC228" t="n">
         <v>0</v>
@@ -37246,16 +37246,16 @@
         <v>0</v>
       </c>
       <c r="AH228" t="n">
-        <v>2103.06599179365</v>
+        <v>2116.13565736214</v>
       </c>
       <c r="AI228" t="n">
-        <v>395.097900112742</v>
+        <v>398.812142047763</v>
       </c>
       <c r="AJ228" t="n">
-        <v>-3035.5589472649</v>
+        <v>-2999.46617711659</v>
       </c>
       <c r="AK228" t="n">
-        <v>-1531.44040318243</v>
+        <v>-1536.18256100372</v>
       </c>
       <c r="AL228" t="n">
         <v>-177.099720923249</v>
@@ -37264,10 +37264,10 @@
         <v>-68.6313761058242</v>
       </c>
       <c r="AN228" t="n">
-        <v>2199.35630169464</v>
+        <v>2202.74937657912</v>
       </c>
       <c r="AO228" t="n">
-        <v>205.391870037787</v>
+        <v>201.381317580914</v>
       </c>
       <c r="AP228" t="n">
         <v>0</v>
@@ -37279,10 +37279,10 @@
         <v>0</v>
       </c>
       <c r="AS228" t="n">
-        <v>32.988</v>
+        <v>33.378</v>
       </c>
       <c r="AT228" t="n">
-        <v>50.6605275</v>
+        <v>46.9143</v>
       </c>
       <c r="AU228" t="n">
         <v>-0.00499800000000003</v>
@@ -37294,13 +37294,13 @@
         <v>-6.55146476</v>
       </c>
       <c r="AX228" t="n">
-        <v>0.1953</v>
+        <v>0.222075</v>
       </c>
       <c r="AY228" t="n">
-        <v>1824.8235472008</v>
+        <v>1838.14695378278</v>
       </c>
       <c r="AZ228" t="n">
-        <v>344.491363240029</v>
+        <v>347.708614073844</v>
       </c>
     </row>
     <row r="229">
@@ -37308,7 +37308,7 @@
         <v>281</v>
       </c>
       <c r="B229" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C229" t="n">
         <v>0</v>
@@ -37332,31 +37332,31 @@
         <v>0.00537181203616477</v>
       </c>
       <c r="J229" t="n">
-        <v>32950.7271435629</v>
+        <v>32986.6653789673</v>
       </c>
       <c r="K229" t="n">
-        <v>22309.3926895551</v>
+        <v>22370.4025687246</v>
       </c>
       <c r="L229" t="n">
         <v>0.06</v>
       </c>
       <c r="M229" t="n">
-        <v>2088.55066124623</v>
+        <v>2097.08359160202</v>
       </c>
       <c r="N229" t="n">
-        <v>445.711641348517</v>
+        <v>418.0795988</v>
       </c>
       <c r="O229" t="n">
         <v>75.1961428571429</v>
       </c>
       <c r="P229" t="n">
-        <v>3498.60397608814</v>
+        <v>3502.99535439423</v>
       </c>
       <c r="Q229" t="n">
-        <v>5281.8898151106</v>
+        <v>5172.44945223095</v>
       </c>
       <c r="R229" t="n">
-        <v>2665.83663901873</v>
+        <v>2678.17662038156</v>
       </c>
       <c r="S229" t="n">
         <v>439.007918245637</v>
@@ -37368,7 +37368,7 @@
         <v>168.612028018865</v>
       </c>
       <c r="V229" t="n">
-        <v>2503.58218013911</v>
+        <v>2510.31568413911</v>
       </c>
       <c r="W229" t="n">
         <v>236.518473484257</v>
@@ -37386,7 +37386,7 @@
         <v>35.7</v>
       </c>
       <c r="AB229" t="n">
-        <v>126.49</v>
+        <v>107.3</v>
       </c>
       <c r="AC229" t="n">
         <v>0</v>
@@ -37404,16 +37404,16 @@
         <v>0</v>
       </c>
       <c r="AH229" t="n">
-        <v>2116.29589098342</v>
+        <v>2130.20400343259</v>
       </c>
       <c r="AI229" t="n">
-        <v>406.074401398579</v>
+        <v>409.328157071834</v>
       </c>
       <c r="AJ229" t="n">
-        <v>-3081.19694687492</v>
+        <v>-3038.47915996096</v>
       </c>
       <c r="AK229" t="n">
-        <v>-1548.65411126325</v>
+        <v>-1554.15264481363</v>
       </c>
       <c r="AL229" t="n">
         <v>-176.976651531437</v>
@@ -37422,7 +37422,7 @@
         <v>-68.4951103731197</v>
       </c>
       <c r="AN229" t="n">
-        <v>2227.71147691042</v>
+        <v>2233.77163051042</v>
       </c>
       <c r="AO229" t="n">
         <v>208.360474114872</v>
@@ -37437,10 +37437,10 @@
         <v>0</v>
       </c>
       <c r="AS229" t="n">
-        <v>32.798</v>
+        <v>33.032</v>
       </c>
       <c r="AT229" t="n">
-        <v>51.52689</v>
+        <v>47.187675</v>
       </c>
       <c r="AU229" t="n">
         <v>-0.028203</v>
@@ -37452,13 +37452,13 @@
         <v>-7.55903602</v>
       </c>
       <c r="AX229" t="n">
-        <v>0.171675</v>
+        <v>0.1953</v>
       </c>
       <c r="AY229" t="n">
-        <v>1861.04264617122</v>
+        <v>1873.06380455511</v>
       </c>
       <c r="AZ229" t="n">
-        <v>352.011017111875</v>
+        <v>355.908999415007</v>
       </c>
     </row>
     <row r="230">
@@ -37466,7 +37466,7 @@
         <v>282</v>
       </c>
       <c r="B230" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C230" t="n">
         <v>0</v>
@@ -37490,31 +37490,31 @@
         <v>0.00535544010784861</v>
       </c>
       <c r="J230" t="n">
-        <v>33286.0255680809</v>
+        <v>33322.3295020527</v>
       </c>
       <c r="K230" t="n">
-        <v>22525.4618651262</v>
+        <v>22587.0626323794</v>
       </c>
       <c r="L230" t="n">
         <v>0.06</v>
       </c>
       <c r="M230" t="n">
-        <v>2100.25739770464</v>
+        <v>2108.83815681017</v>
       </c>
       <c r="N230" t="n">
-        <v>448.845865348848</v>
+        <v>420.941553051321</v>
       </c>
       <c r="O230" t="n">
         <v>75.1961428571429</v>
       </c>
       <c r="P230" t="n">
-        <v>3530.56904667102</v>
+        <v>3535.00054689959</v>
       </c>
       <c r="Q230" t="n">
-        <v>5525.38508018273</v>
+        <v>5414.38765699182</v>
       </c>
       <c r="R230" t="n">
-        <v>2691.32700501131</v>
+        <v>2703.7773350445</v>
       </c>
       <c r="S230" t="n">
         <v>443.111839208704</v>
@@ -37526,7 +37526,7 @@
         <v>168.095640889683</v>
       </c>
       <c r="V230" t="n">
-        <v>2565.57593301876</v>
+        <v>2572.28030761076</v>
       </c>
       <c r="W230" t="n">
         <v>239.93696178451</v>
@@ -37544,7 +37544,7 @@
         <v>36.7</v>
       </c>
       <c r="AB230" t="n">
-        <v>126.49</v>
+        <v>107.3</v>
       </c>
       <c r="AC230" t="n">
         <v>0</v>
@@ -37562,16 +37562,16 @@
         <v>0</v>
       </c>
       <c r="AH230" t="n">
-        <v>2143.53144509877</v>
+        <v>2156.6491004609</v>
       </c>
       <c r="AI230" t="n">
-        <v>408.43534654845</v>
+        <v>412.861482268104</v>
       </c>
       <c r="AJ230" t="n">
-        <v>-3146.40549129785</v>
+        <v>-3096.94064785277</v>
       </c>
       <c r="AK230" t="n">
-        <v>-1565.73275498582</v>
+        <v>-1571.99262396792</v>
       </c>
       <c r="AL230" t="n">
         <v>-176.003712838393</v>
@@ -37580,7 +37580,7 @@
         <v>-68.3249650694424</v>
       </c>
       <c r="AN230" t="n">
-        <v>2255.1140314319</v>
+        <v>2261.1676309151</v>
       </c>
       <c r="AO230" t="n">
         <v>211.371984516169</v>
@@ -37595,10 +37595,10 @@
         <v>0</v>
       </c>
       <c r="AS230" t="n">
-        <v>32.919</v>
+        <v>33.049</v>
       </c>
       <c r="AT230" t="n">
-        <v>52.4330775</v>
+        <v>47.4462</v>
       </c>
       <c r="AU230" t="n">
         <v>-0.051408</v>
@@ -37610,13 +37610,13 @@
         <v>-8.5404791</v>
       </c>
       <c r="AX230" t="n">
-        <v>0.14805</v>
+        <v>0.171675</v>
       </c>
       <c r="AY230" t="n">
-        <v>1893.20808111612</v>
+        <v>1905.18789737379</v>
       </c>
       <c r="AZ230" t="n">
-        <v>358.772497470056</v>
+        <v>362.401059696363</v>
       </c>
     </row>
     <row r="231">
@@ -37624,7 +37624,7 @@
         <v>283</v>
       </c>
       <c r="B231" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C231" t="n">
         <v>0</v>
@@ -37648,31 +37648,31 @@
         <v>0.00531873576798692</v>
       </c>
       <c r="J231" t="n">
-        <v>33620.9223173374</v>
+        <v>33657.5915117831</v>
       </c>
       <c r="K231" t="n">
-        <v>22733.4209372584</v>
+        <v>22795.5904137562</v>
       </c>
       <c r="L231" t="n">
         <v>0.06</v>
       </c>
       <c r="M231" t="n">
-        <v>2111.12558926885</v>
+        <v>2119.75075118607</v>
       </c>
       <c r="N231" t="n">
-        <v>452.010972132469</v>
+        <v>423.831707301406</v>
       </c>
       <c r="O231" t="n">
         <v>75.1961428571429</v>
       </c>
       <c r="P231" t="n">
-        <v>3562.45678888173</v>
+        <v>3566.92831397173</v>
       </c>
       <c r="Q231" t="n">
-        <v>5555.56109348086</v>
+        <v>5444.65422431546</v>
       </c>
       <c r="R231" t="n">
-        <v>2716.85875196385</v>
+        <v>2729.4359962967</v>
       </c>
       <c r="S231" t="n">
         <v>447.254124325517</v>
@@ -37684,7 +37684,7 @@
         <v>168.174727206765</v>
       </c>
       <c r="V231" t="n">
-        <v>2589.14544571579</v>
+        <v>2595.84982030779</v>
       </c>
       <c r="W231" t="n">
         <v>243.404858750762</v>
@@ -37702,7 +37702,7 @@
         <v>37.7</v>
       </c>
       <c r="AB231" t="n">
-        <v>126.49</v>
+        <v>107.3</v>
       </c>
       <c r="AC231" t="n">
         <v>0</v>
@@ -37720,16 +37720,16 @@
         <v>0</v>
       </c>
       <c r="AH231" t="n">
-        <v>2171.23672120873</v>
+        <v>2184.82873108931</v>
       </c>
       <c r="AI231" t="n">
-        <v>410.774203006256</v>
+        <v>415.112888561561</v>
       </c>
       <c r="AJ231" t="n">
-        <v>-3200.63543360892</v>
+        <v>-3144.42818763676</v>
       </c>
       <c r="AK231" t="n">
-        <v>-1582.37560688035</v>
+        <v>-1589.40434630063</v>
       </c>
       <c r="AL231" t="n">
         <v>-174.402183649244</v>
@@ -37738,7 +37738,7 @@
         <v>-68.2441226430012</v>
       </c>
       <c r="AN231" t="n">
-        <v>2283.00791644657</v>
+        <v>2289.05496181297</v>
       </c>
       <c r="AO231" t="n">
         <v>214.42702138253</v>
@@ -37753,10 +37753,10 @@
         <v>0</v>
       </c>
       <c r="AS231" t="n">
-        <v>33.169</v>
+        <v>33.299</v>
       </c>
       <c r="AT231" t="n">
-        <v>53.311815</v>
+        <v>47.677275</v>
       </c>
       <c r="AU231" t="n">
         <v>-0.074613</v>
@@ -37768,13 +37768,13 @@
         <v>-9.38594716</v>
       </c>
       <c r="AX231" t="n">
-        <v>0.124425</v>
+        <v>0.14805</v>
       </c>
       <c r="AY231" t="n">
-        <v>1920.17926104403</v>
+        <v>1932.25893577761</v>
       </c>
       <c r="AZ231" t="n">
-        <v>364.585916489856</v>
+        <v>368.125800738584</v>
       </c>
     </row>
     <row r="232">
@@ -37782,7 +37782,7 @@
         <v>284</v>
       </c>
       <c r="B232" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C232" t="n">
         <v>0</v>
@@ -37806,31 +37806,31 @@
         <v>0.00528246336028104</v>
       </c>
       <c r="J232" t="n">
-        <v>33961.1412638085</v>
+        <v>33998.1815234672</v>
       </c>
       <c r="K232" t="n">
-        <v>22952.6941043116</v>
+        <v>23015.4632309036</v>
       </c>
       <c r="L232" t="n">
         <v>0</v>
       </c>
       <c r="M232" t="n">
-        <v>2122.59027309071</v>
+        <v>2131.26227483347</v>
       </c>
       <c r="N232" t="n">
-        <v>455.207266</v>
+        <v>426.750339416305</v>
       </c>
       <c r="O232" t="n">
         <v>75.1961428571429</v>
       </c>
       <c r="P232" t="n">
-        <v>3593.20995830302</v>
+        <v>3597.72008416121</v>
       </c>
       <c r="Q232" t="n">
-        <v>5585.99080118651</v>
+        <v>5475.17125667803</v>
       </c>
       <c r="R232" t="n">
-        <v>2743.44509061594</v>
+        <v>2756.14926865522</v>
       </c>
       <c r="S232" t="n">
         <v>451.435132230733</v>
@@ -37842,7 +37842,7 @@
         <v>167.960728937013</v>
       </c>
       <c r="V232" t="n">
-        <v>2612.832397716</v>
+        <v>2619.536772308</v>
       </c>
       <c r="W232" t="n">
         <v>246.922878504595</v>
@@ -37860,7 +37860,7 @@
         <v>38.7</v>
       </c>
       <c r="AB232" t="n">
-        <v>126.49</v>
+        <v>107.3</v>
       </c>
       <c r="AC232" t="n">
         <v>0</v>
@@ -37878,16 +37878,16 @@
         <v>0</v>
       </c>
       <c r="AH232" t="n">
-        <v>2199.78525175876</v>
+        <v>2213.78433861144</v>
       </c>
       <c r="AI232" t="n">
-        <v>413.724405651562</v>
+        <v>418.04796048695</v>
       </c>
       <c r="AJ232" t="n">
-        <v>-3236.52722494034</v>
+        <v>-3173.68147901862</v>
       </c>
       <c r="AK232" t="n">
-        <v>-1598.69339745359</v>
+        <v>-1606.49961843659</v>
       </c>
       <c r="AL232" t="n">
         <v>-173.096688056935</v>
@@ -37896,7 +37896,7 @@
         <v>-68.1728136075684</v>
       </c>
       <c r="AN232" t="n">
-        <v>2311.00559023267</v>
+        <v>2317.04608148227</v>
       </c>
       <c r="AO232" t="n">
         <v>217.526213817928</v>
@@ -37911,10 +37911,10 @@
         <v>0</v>
       </c>
       <c r="AS232" t="n">
-        <v>33.587</v>
+        <v>33.691</v>
       </c>
       <c r="AT232" t="n">
-        <v>54.1586025</v>
+        <v>47.8764</v>
       </c>
       <c r="AU232" t="n">
         <v>-0.097818</v>
@@ -37926,13 +37926,13 @@
         <v>-7.4295444</v>
       </c>
       <c r="AX232" t="n">
-        <v>0.1008</v>
+        <v>0.124425</v>
       </c>
       <c r="AY232" t="n">
-        <v>1941.94109453618</v>
+        <v>1954.2298890587</v>
       </c>
       <c r="AZ232" t="n">
-        <v>368.776880236091</v>
+        <v>372.453859887401</v>
       </c>
     </row>
     <row r="233">
@@ -37940,7 +37940,7 @@
         <v>285</v>
       </c>
       <c r="B233" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C233" t="n">
         <v>0</v>
@@ -37964,46 +37964,46 @@
         <v>0.00523852479905496</v>
       </c>
       <c r="J233" t="n">
-        <v>34301.5610479103</v>
+        <v>34338.9725918288</v>
       </c>
       <c r="K233" t="n">
-        <v>23169.9647766885</v>
+        <v>23233.3280771181</v>
       </c>
       <c r="L233" t="n">
         <v>0</v>
       </c>
       <c r="M233" t="n">
-        <v>0</v>
+        <v>2137.26831123599</v>
       </c>
       <c r="N233" t="n">
-        <v>0</v>
+        <v>429.69773</v>
       </c>
       <c r="O233" t="n">
-        <v>0</v>
+        <v>75.1961428571429</v>
       </c>
       <c r="P233" t="n">
-        <v>0</v>
+        <v>3628.38316225891</v>
       </c>
       <c r="Q233" t="n">
-        <v>0</v>
+        <v>5505.17271796864</v>
       </c>
       <c r="R233" t="n">
-        <v>0</v>
+        <v>2783.20121523231</v>
       </c>
       <c r="S233" t="n">
-        <v>0</v>
+        <v>455.65522491159</v>
       </c>
       <c r="T233" t="n">
-        <v>0</v>
+        <v>50.6890505411461</v>
       </c>
       <c r="U233" t="n">
-        <v>0</v>
+        <v>169.128415148048</v>
       </c>
       <c r="V233" t="n">
-        <v>0</v>
+        <v>2621.69760485406</v>
       </c>
       <c r="W233" t="n">
-        <v>0</v>
+        <v>250.491745489055</v>
       </c>
       <c r="X233" t="n">
         <v>0</v>
@@ -38015,10 +38015,10 @@
         <v>0</v>
       </c>
       <c r="AA233" t="n">
-        <v>0</v>
+        <v>39.7</v>
       </c>
       <c r="AB233" t="n">
-        <v>0</v>
+        <v>107.3</v>
       </c>
       <c r="AC233" t="n">
         <v>0</v>
@@ -38036,28 +38036,28 @@
         <v>0</v>
       </c>
       <c r="AH233" t="n">
-        <v>0</v>
+        <v>2220.46890900036</v>
       </c>
       <c r="AI233" t="n">
-        <v>0</v>
+        <v>421.53848883758</v>
       </c>
       <c r="AJ233" t="n">
-        <v>-2590.42455572159</v>
+        <v>-3199.40895171593</v>
       </c>
       <c r="AK233" t="n">
-        <v>-1282.9310696022</v>
+        <v>-1622.85360448667</v>
       </c>
       <c r="AL233" t="n">
-        <v>-156.143354723602</v>
+        <v>-171.331862220655</v>
       </c>
       <c r="AM233" t="n">
-        <v>-62.3661469409017</v>
+        <v>-68.00376077917</v>
       </c>
       <c r="AN233" t="n">
-        <v>1747.69959970137</v>
+        <v>2342.10701364314</v>
       </c>
       <c r="AO233" t="n">
-        <v>164.30955728397</v>
+        <v>220.670200019007</v>
       </c>
       <c r="AP233" t="n">
         <v>0</v>
@@ -38069,10 +38069,10 @@
         <v>0</v>
       </c>
       <c r="AS233" t="n">
-        <v>26.327</v>
+        <v>34.267</v>
       </c>
       <c r="AT233" t="n">
-        <v>48.724065</v>
+        <v>48.267</v>
       </c>
       <c r="AU233" t="n">
         <v>-0.082501</v>
@@ -38084,13 +38084,13 @@
         <v>-5.6954214</v>
       </c>
       <c r="AX233" t="n">
-        <v>0.0819</v>
+        <v>0.1008</v>
       </c>
       <c r="AY233" t="n">
-        <v>1465.77451906491</v>
+        <v>1974.53949281145</v>
       </c>
       <c r="AZ233" t="n">
-        <v>277.41013992141</v>
+        <v>375.201184534694</v>
       </c>
     </row>
     <row r="234">
@@ -38098,7 +38098,7 @@
         <v>286</v>
       </c>
       <c r="B234" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C234" t="n">
         <v>0</v>
@@ -38122,10 +38122,10 @@
         <v>0.00520317743921583</v>
       </c>
       <c r="J234" t="n">
-        <v>34643.9892083195</v>
+        <v>34681.7742269654</v>
       </c>
       <c r="K234" t="n">
-        <v>23394.6446793677</v>
+        <v>23458.6224157841</v>
       </c>
       <c r="L234" t="n">
         <v>0</v>
@@ -38200,22 +38200,22 @@
         <v>0</v>
       </c>
       <c r="AJ234" t="n">
-        <v>-1944.88405079989</v>
+        <v>-2565.89446393977</v>
       </c>
       <c r="AK234" t="n">
-        <v>-963.813334676812</v>
+        <v>-1302.25891073748</v>
       </c>
       <c r="AL234" t="n">
-        <v>-140.503354723602</v>
+        <v>-155.691862220655</v>
       </c>
       <c r="AM234" t="n">
-        <v>-56.219480274235</v>
+        <v>-61.8570941125033</v>
       </c>
       <c r="AN234" t="n">
-        <v>1170.44501477215</v>
+        <v>1763.34394443072</v>
       </c>
       <c r="AO234" t="n">
-        <v>110.323740882455</v>
+        <v>166.684383617493</v>
       </c>
       <c r="AP234" t="n">
         <v>0</v>
@@ -38227,10 +38227,10 @@
         <v>0</v>
       </c>
       <c r="AS234" t="n">
-        <v>20.148</v>
+        <v>26.897</v>
       </c>
       <c r="AT234" t="n">
-        <v>43.9508475</v>
+        <v>43.07175</v>
       </c>
       <c r="AU234" t="n">
         <v>-0.067184</v>
@@ -38242,13 +38242,13 @@
         <v>-4.0712984</v>
       </c>
       <c r="AX234" t="n">
-        <v>0.063</v>
+        <v>0.0819</v>
       </c>
       <c r="AY234" t="n">
-        <v>983.479943917686</v>
+        <v>1489.29344520775</v>
       </c>
       <c r="AZ234" t="n">
-        <v>185.512186948009</v>
+        <v>282.30735102437</v>
       </c>
     </row>
     <row r="235">
@@ -38256,7 +38256,7 @@
         <v>287</v>
       </c>
       <c r="B235" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C235" t="n">
         <v>0</v>
@@ -38280,10 +38280,10 @@
         <v>0.00518825436858217</v>
       </c>
       <c r="J235" t="n">
-        <v>34982.5010349293</v>
+        <v>35020.6552568908</v>
       </c>
       <c r="K235" t="n">
-        <v>23613.4172227518</v>
+        <v>23677.9932401983</v>
       </c>
       <c r="L235" t="n">
         <v>0</v>
@@ -38358,22 +38358,22 @@
         <v>0</v>
       </c>
       <c r="AJ235" t="n">
-        <v>-1632.11327259664</v>
+        <v>-1929.3211494383</v>
       </c>
       <c r="AK235" t="n">
-        <v>-807.322646075382</v>
+        <v>-978.05172718766</v>
       </c>
       <c r="AL235" t="n">
-        <v>-124.846688056935</v>
+        <v>-140.035195553988</v>
       </c>
       <c r="AM235" t="n">
-        <v>-50.1194802742351</v>
+        <v>-55.7570941125033</v>
       </c>
       <c r="AN235" t="n">
-        <v>587.8872894861</v>
+        <v>1179.27773486146</v>
       </c>
       <c r="AO235" t="n">
-        <v>55.5576476635339</v>
+        <v>111.918290398571</v>
       </c>
       <c r="AP235" t="n">
         <v>0</v>
@@ -38385,10 +38385,10 @@
         <v>0</v>
       </c>
       <c r="AS235" t="n">
-        <v>14.246</v>
+        <v>20.598</v>
       </c>
       <c r="AT235" t="n">
-        <v>39.2606325</v>
+        <v>38.399175</v>
       </c>
       <c r="AU235" t="n">
         <v>-0.051867</v>
@@ -38400,13 +38400,13 @@
         <v>-2.53</v>
       </c>
       <c r="AX235" t="n">
-        <v>0.0441</v>
+        <v>0.063</v>
       </c>
       <c r="AY235" t="n">
-        <v>494.951681645722</v>
+        <v>997.706980712655</v>
       </c>
       <c r="AZ235" t="n">
-        <v>93.0879912716015</v>
+        <v>188.906951098019</v>
       </c>
     </row>
     <row r="236">
@@ -38414,7 +38414,7 @@
         <v>288</v>
       </c>
       <c r="B236" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C236" t="n">
         <v>0</v>
@@ -38438,10 +38438,10 @@
         <v>0.0051614753216962</v>
       </c>
       <c r="J236" t="n">
-        <v>35315.7910831399</v>
+        <v>35354.3088132011</v>
       </c>
       <c r="K236" t="n">
-        <v>23832.3900156036</v>
+        <v>23897.5648617057</v>
       </c>
       <c r="L236" t="n">
         <v>0</v>
@@ -38516,22 +38516,22 @@
         <v>0</v>
       </c>
       <c r="AJ236" t="n">
-        <v>-1316.92960739764</v>
+        <v>-1620.71011849109</v>
       </c>
       <c r="AK236" t="n">
-        <v>-649.04804919659</v>
+        <v>-819.044426136617</v>
       </c>
       <c r="AL236" t="n">
-        <v>-117.896688056935</v>
+        <v>-133.085195553988</v>
       </c>
       <c r="AM236" t="n">
-        <v>-44.5628136075684</v>
+        <v>-50.2004274458367</v>
       </c>
       <c r="AN236" t="n">
-        <v>0</v>
+        <v>589.881961092164</v>
       </c>
       <c r="AO236" t="n">
-        <v>0</v>
+        <v>56.3606427350373</v>
       </c>
       <c r="AP236" t="n">
         <v>0</v>
@@ -38543,10 +38543,10 @@
         <v>0</v>
       </c>
       <c r="AS236" t="n">
-        <v>8.631</v>
+        <v>14.586</v>
       </c>
       <c r="AT236" t="n">
-        <v>34.78752</v>
+        <v>33.900525</v>
       </c>
       <c r="AU236" t="n">
         <v>-0.03655</v>
@@ -38558,13 +38558,13 @@
         <v>-1.54</v>
       </c>
       <c r="AX236" t="n">
-        <v>0.0252</v>
+        <v>0.0441</v>
       </c>
       <c r="AY236" t="n">
-        <v>0</v>
+        <v>499.605504525081</v>
       </c>
       <c r="AZ236" t="n">
-        <v>0</v>
+        <v>94.8461599884554</v>
       </c>
     </row>
     <row r="237">
@@ -38572,7 +38572,7 @@
         <v>289</v>
       </c>
       <c r="B237" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C237" t="n">
         <v>0</v>
@@ -38596,10 +38596,10 @@
         <v>0.00510723610962516</v>
       </c>
       <c r="J237" t="n">
-        <v>35651.4911829193</v>
+        <v>35690.3750496415</v>
       </c>
       <c r="K237" t="n">
-        <v>24049.8609374481</v>
+        <v>24115.6305050135</v>
       </c>
       <c r="L237" t="n">
         <v>0</v>
@@ -38674,16 +38674,16 @@
         <v>0</v>
       </c>
       <c r="AJ237" t="n">
-        <v>-1000.01621849101</v>
+        <v>-1310.36315135724</v>
       </c>
       <c r="AK237" t="n">
-        <v>-489.097850855465</v>
+        <v>-658.353828913723</v>
       </c>
       <c r="AL237" t="n">
-        <v>-102.639460927823</v>
+        <v>-117.827968424876</v>
       </c>
       <c r="AM237" t="n">
-        <v>-39.1257068437845</v>
+        <v>-44.7633206820528</v>
       </c>
       <c r="AN237" t="n">
         <v>0</v>
@@ -38701,10 +38701,10 @@
         <v>0</v>
       </c>
       <c r="AS237" t="n">
-        <v>5.288</v>
+        <v>8.861</v>
       </c>
       <c r="AT237" t="n">
-        <v>30.7721925</v>
+        <v>30.096</v>
       </c>
       <c r="AU237" t="n">
         <v>0</v>
@@ -38716,7 +38716,7 @@
         <v>-0.99</v>
       </c>
       <c r="AX237" t="n">
-        <v>0.0189</v>
+        <v>0.0252</v>
       </c>
       <c r="AY237" t="n">
         <v>0</v>
@@ -38730,7 +38730,7 @@
         <v>290</v>
       </c>
       <c r="B238" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C238" t="n">
         <v>0</v>
@@ -38754,10 +38754,10 @@
         <v>0.00504186442548771</v>
       </c>
       <c r="J238" t="n">
-        <v>35990.5051036059</v>
+        <v>36029.7587212606</v>
       </c>
       <c r="K238" t="n">
-        <v>24277.3443326741</v>
+        <v>24343.7360029856</v>
       </c>
       <c r="L238" t="n">
         <v>0</v>
@@ -38832,16 +38832,16 @@
         <v>0</v>
       </c>
       <c r="AJ238" t="n">
-        <v>-668.493113680042</v>
+        <v>-985.499891937728</v>
       </c>
       <c r="AK238" t="n">
-        <v>-327.618230554787</v>
+        <v>-496.127188811054</v>
       </c>
       <c r="AL238" t="n">
-        <v>-87.8054250901435</v>
+        <v>-102.993932587196</v>
       </c>
       <c r="AM238" t="n">
-        <v>-33.5781893785058</v>
+        <v>-39.2158032167741</v>
       </c>
       <c r="AN238" t="n">
         <v>0</v>
@@ -38859,10 +38859,10 @@
         <v>0</v>
       </c>
       <c r="AS238" t="n">
-        <v>3.443</v>
+        <v>5.428</v>
       </c>
       <c r="AT238" t="n">
-        <v>26.678565</v>
+        <v>26.477325</v>
       </c>
       <c r="AU238" t="n">
         <v>0</v>
@@ -38874,7 +38874,7 @@
         <v>-0.44</v>
       </c>
       <c r="AX238" t="n">
-        <v>0.0126</v>
+        <v>0.0189</v>
       </c>
       <c r="AY238" t="n">
         <v>0</v>
@@ -38888,7 +38888,7 @@
         <v>291</v>
       </c>
       <c r="B239" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C239" t="n">
         <v>0</v>
@@ -38912,10 +38912,10 @@
         <v>0.00497734894393131</v>
       </c>
       <c r="J239" t="n">
-        <v>36329.4186054772</v>
+        <v>36369.041864541</v>
       </c>
       <c r="K239" t="n">
-        <v>24509.8339645908</v>
+        <v>24576.8614282898</v>
       </c>
       <c r="L239" t="n">
         <v>0</v>
@@ -38990,16 +38990,16 @@
         <v>0</v>
       </c>
       <c r="AJ239" t="n">
-        <v>-335.159448071191</v>
+        <v>-658.8206384788</v>
       </c>
       <c r="AK239" t="n">
-        <v>-164.606705436956</v>
+        <v>-332.361029033251</v>
       </c>
       <c r="AL239" t="n">
-        <v>-73.3828424431519</v>
+        <v>-88.5713499402048</v>
       </c>
       <c r="AM239" t="n">
-        <v>-28.013459008921</v>
+        <v>-33.6510728471892</v>
       </c>
       <c r="AN239" t="n">
         <v>0</v>
@@ -39017,10 +39017,10 @@
         <v>0</v>
       </c>
       <c r="AS239" t="n">
-        <v>1.548</v>
+        <v>3.533</v>
       </c>
       <c r="AT239" t="n">
-        <v>22.4751375</v>
+        <v>22.74885</v>
       </c>
       <c r="AU239" t="n">
         <v>0</v>
@@ -39032,7 +39032,7 @@
         <v>0</v>
       </c>
       <c r="AX239" t="n">
-        <v>0.0063</v>
+        <v>0.0126</v>
       </c>
       <c r="AY239" t="n">
         <v>0</v>
@@ -39046,7 +39046,7 @@
         <v>292</v>
       </c>
       <c r="B240" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C240" t="n">
         <v>0</v>
@@ -39070,10 +39070,10 @@
         <v>0.00499562882477833</v>
       </c>
       <c r="J240" t="n">
-        <v>36672.0476035171</v>
+        <v>36712.0445563551</v>
       </c>
       <c r="K240" t="n">
-        <v>24747.7303321334</v>
+        <v>24815.4083751127</v>
       </c>
       <c r="L240" t="n">
         <v>0</v>
@@ -39148,16 +39148,16 @@
         <v>0</v>
       </c>
       <c r="AJ240" t="n">
-        <v>0</v>
+        <v>-330.310363078119</v>
       </c>
       <c r="AK240" t="n">
-        <v>0</v>
+        <v>-166.992072913939</v>
       </c>
       <c r="AL240" t="n">
-        <v>-59.3603004670196</v>
+        <v>-74.5488079640726</v>
       </c>
       <c r="AM240" t="n">
-        <v>-22.4281041684108</v>
+        <v>-28.0657180066791</v>
       </c>
       <c r="AN240" t="n">
         <v>0</v>
@@ -39175,10 +39175,10 @@
         <v>0</v>
       </c>
       <c r="AS240" t="n">
-        <v>0</v>
+        <v>1.588</v>
       </c>
       <c r="AT240" t="n">
-        <v>18.23391</v>
+        <v>18.982575</v>
       </c>
       <c r="AU240" t="n">
         <v>0</v>
@@ -39190,7 +39190,7 @@
         <v>0</v>
       </c>
       <c r="AX240" t="n">
-        <v>0</v>
+        <v>0.0063</v>
       </c>
       <c r="AY240" t="n">
         <v>0</v>
@@ -39204,7 +39204,7 @@
         <v>293</v>
       </c>
       <c r="B241" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C241" t="n">
         <v>0</v>
@@ -39228,10 +39228,10 @@
         <v>0.00506011557102015</v>
       </c>
       <c r="J241" t="n">
-        <v>37019.8983799563</v>
+        <v>37060.2747217842</v>
       </c>
       <c r="K241" t="n">
-        <v>24989.6316890286</v>
+        <v>25057.9712638013</v>
       </c>
       <c r="L241" t="n">
         <v>0</v>
@@ -39312,10 +39312,10 @@
         <v>0</v>
       </c>
       <c r="AL241" t="n">
-        <v>-44.7267031921651</v>
+        <v>-59.9152106892181</v>
       </c>
       <c r="AM241" t="n">
-        <v>-16.8077032344487</v>
+        <v>-22.4453170727169</v>
       </c>
       <c r="AN241" t="n">
         <v>0</v>
@@ -39336,7 +39336,7 @@
         <v>0</v>
       </c>
       <c r="AT241" t="n">
-        <v>14.79933</v>
+        <v>15.4512</v>
       </c>
       <c r="AU241" t="n">
         <v>0</v>
@@ -39362,7 +39362,7 @@
         <v>294</v>
       </c>
       <c r="B242" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C242" t="n">
         <v>0</v>
@@ -39386,10 +39386,10 @@
         <v>0.00505782301096946</v>
       </c>
       <c r="J242" t="n">
-        <v>37370.4604644104</v>
+        <v>37411.2191523595</v>
       </c>
       <c r="K242" t="n">
-        <v>25243.9485129168</v>
+        <v>25312.9835722735</v>
       </c>
       <c r="L242" t="n">
         <v>0</v>
@@ -39470,10 +39470,10 @@
         <v>0</v>
       </c>
       <c r="AL242" t="n">
-        <v>-29.956308551875</v>
+        <v>-45.1448160489279</v>
       </c>
       <c r="AM242" t="n">
-        <v>-11.2045152047926</v>
+        <v>-16.8421290430608</v>
       </c>
       <c r="AN242" t="n">
         <v>0</v>
@@ -39494,7 +39494,7 @@
         <v>0</v>
       </c>
       <c r="AT242" t="n">
-        <v>11.3841</v>
+        <v>12.5541</v>
       </c>
       <c r="AU242" t="n">
         <v>0</v>
@@ -39520,7 +39520,7 @@
         <v>295</v>
       </c>
       <c r="B243" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C243" t="n">
         <v>0</v>
@@ -39544,10 +39544,10 @@
         <v>0.00499008134832168</v>
       </c>
       <c r="J243" t="n">
-        <v>37722.1271558336</v>
+        <v>37763.2693946611</v>
       </c>
       <c r="K243" t="n">
-        <v>25496.8635905316</v>
+        <v>25566.5903010928</v>
       </c>
       <c r="L243" t="n">
         <v>0</v>
@@ -39628,10 +39628,10 @@
         <v>0</v>
       </c>
       <c r="AL243" t="n">
-        <v>-15.0478377410244</v>
+        <v>-30.2363452380774</v>
       </c>
       <c r="AM243" t="n">
-        <v>-5.59869096456711</v>
+        <v>-11.2363048028354</v>
       </c>
       <c r="AN243" t="n">
         <v>0</v>
@@ -39652,7 +39652,7 @@
         <v>0</v>
       </c>
       <c r="AT243" t="n">
-        <v>7.96887</v>
+        <v>9.657</v>
       </c>
       <c r="AU243" t="n">
         <v>0</v>
@@ -39678,7 +39678,7 @@
         <v>296</v>
       </c>
       <c r="B244" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C244" t="n">
         <v>0</v>
@@ -39702,10 +39702,10 @@
         <v>0.0049691294268861</v>
       </c>
       <c r="J244" t="n">
-        <v>38076.6055740871</v>
+        <v>38118.1344304476</v>
       </c>
       <c r="K244" t="n">
-        <v>25752.5821606932</v>
+        <v>25823.0081892181</v>
       </c>
       <c r="L244" t="n">
         <v>0</v>
@@ -39786,10 +39786,10 @@
         <v>0</v>
       </c>
       <c r="AL244" t="n">
-        <v>0</v>
+        <v>-15.188507497053</v>
       </c>
       <c r="AM244" t="n">
-        <v>0</v>
+        <v>-5.63761383826826</v>
       </c>
       <c r="AN244" t="n">
         <v>0</v>
@@ -39810,7 +39810,7 @@
         <v>0</v>
       </c>
       <c r="AT244" t="n">
-        <v>4.55364</v>
+        <v>6.7599</v>
       </c>
       <c r="AU244" t="n">
         <v>0</v>
@@ -39836,7 +39836,7 @@
         <v>297</v>
       </c>
       <c r="B245" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C245" t="n">
         <v>0</v>
@@ -39860,10 +39860,10 @@
         <v>0.00493313996642741</v>
       </c>
       <c r="J245" t="n">
-        <v>38433.0923686479</v>
+        <v>38475.0100330092</v>
       </c>
       <c r="K245" t="n">
-        <v>26005.3971135742</v>
+        <v>26076.5145194908</v>
       </c>
       <c r="L245" t="n">
         <v>0</v>
@@ -39968,7 +39968,7 @@
         <v>0</v>
       </c>
       <c r="AT245" t="n">
-        <v>3.41523</v>
+        <v>3.8628</v>
       </c>
       <c r="AU245" t="n">
         <v>0</v>
@@ -39994,7 +39994,7 @@
         <v>298</v>
       </c>
       <c r="B246" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C246" t="n">
         <v>0</v>
@@ -40018,10 +40018,10 @@
         <v>0.00490892355942396</v>
       </c>
       <c r="J246" t="n">
-        <v>38792.9934029314</v>
+        <v>38835.3035990882</v>
       </c>
       <c r="K246" t="n">
-        <v>26263.4185526135</v>
+        <v>26335.2415741888</v>
       </c>
       <c r="L246" t="n">
         <v>0</v>
@@ -40126,7 +40126,7 @@
         <v>0</v>
       </c>
       <c r="AT246" t="n">
-        <v>2.27682</v>
+        <v>2.8971</v>
       </c>
       <c r="AU246" t="n">
         <v>0</v>
@@ -40152,7 +40152,7 @@
         <v>299</v>
       </c>
       <c r="B247" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C247" t="n">
         <v>0</v>
@@ -40176,10 +40176,10 @@
         <v>0.00486986675712853</v>
       </c>
       <c r="J247" t="n">
-        <v>39155.6057452298</v>
+        <v>39198.3114303136</v>
       </c>
       <c r="K247" t="n">
-        <v>26513.7303871491</v>
+        <v>26586.2379407954</v>
       </c>
       <c r="L247" t="n">
         <v>0</v>
@@ -40284,7 +40284,7 @@
         <v>0</v>
       </c>
       <c r="AT247" t="n">
-        <v>1.13841</v>
+        <v>1.9314</v>
       </c>
       <c r="AU247" t="n">
         <v>0</v>
@@ -40310,7 +40310,7 @@
         <v>300</v>
       </c>
       <c r="B248" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C248" t="n">
         <v>0</v>
@@ -40334,10 +40334,10 @@
         <v>0.00479750334774942</v>
       </c>
       <c r="J248" t="n">
-        <v>39519.9252073895</v>
+        <v>39563.0282432976</v>
       </c>
       <c r="K248" t="n">
-        <v>26764.7430948214</v>
+        <v>26837.9370972285</v>
       </c>
       <c r="L248" t="n">
         <v>0</v>
@@ -40442,7 +40442,7 @@
         <v>0</v>
       </c>
       <c r="AT248" t="n">
-        <v>0</v>
+        <v>0.9657</v>
       </c>
       <c r="AU248" t="n">
         <v>0</v>
@@ -40468,7 +40468,7 @@
         <v>301</v>
       </c>
       <c r="B249" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C249" t="n">
         <v>0</v>
@@ -40492,10 +40492,10 @@
         <v>0.00475966491958957</v>
       </c>
       <c r="J249" t="n">
-        <v>39886.9559775642</v>
+        <v>39930.4593214279</v>
       </c>
       <c r="K249" t="n">
-        <v>27014.6544304218</v>
+        <v>27088.5318696485</v>
       </c>
       <c r="L249" t="n">
         <v>0</v>
@@ -40626,7 +40626,7 @@
         <v>302</v>
       </c>
       <c r="B250" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C250" t="n">
         <v>0</v>
@@ -40650,10 +40650,10 @@
         <v>0.00472225627993206</v>
       </c>
       <c r="J250" t="n">
-        <v>40256.7984745692</v>
+        <v>40300.7051930432</v>
       </c>
       <c r="K250" t="n">
-        <v>27272.0751210582</v>
+        <v>27346.6565330667</v>
       </c>
       <c r="L250" t="n">
         <v>0</v>
@@ -40784,7 +40784,7 @@
         <v>303</v>
       </c>
       <c r="B251" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C251" t="n">
         <v>0</v>
@@ -40808,10 +40808,10 @@
         <v>0.00467787384162532</v>
       </c>
       <c r="J251" t="n">
-        <v>40629.9547924814</v>
+        <v>40674.2684998372</v>
       </c>
       <c r="K251" t="n">
-        <v>27534.5020483853</v>
+        <v>27609.801123817</v>
       </c>
       <c r="L251" t="n">
         <v>0</v>
@@ -40942,7 +40942,7 @@
         <v>304</v>
       </c>
       <c r="B252" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C252" t="n">
         <v>0</v>
@@ -40966,10 +40966,10 @@
         <v>0.00464505110660429</v>
       </c>
       <c r="J252" t="n">
-        <v>41007.1278630083</v>
+        <v>41051.8529401812</v>
       </c>
       <c r="K252" t="n">
-        <v>27793.0241110937</v>
+        <v>27869.0301712483</v>
       </c>
       <c r="L252" t="n">
         <v>0</v>
@@ -41100,7 +41100,7 @@
         <v>305</v>
       </c>
       <c r="B253" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C253" t="n">
         <v>0</v>
@@ -41124,10 +41124,10 @@
         <v>0.0046235743673726</v>
       </c>
       <c r="J253" t="n">
-        <v>41388.8197802269</v>
+        <v>41433.9611557689</v>
       </c>
       <c r="K253" t="n">
-        <v>28052.9479200755</v>
+        <v>28129.6647983326</v>
       </c>
       <c r="L253" t="n">
         <v>0</v>
@@ -41258,7 +41258,7 @@
         <v>306</v>
       </c>
       <c r="B254" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C254" t="n">
         <v>0</v>
@@ -41282,10 +41282,10 @@
         <v>0.00459864848601987</v>
       </c>
       <c r="J254" t="n">
-        <v>41774.4280312449</v>
+        <v>41819.9899765679</v>
       </c>
       <c r="K254" t="n">
-        <v>28323.9855745107</v>
+        <v>28401.4436640942</v>
       </c>
       <c r="L254" t="n">
         <v>0</v>
@@ -41416,7 +41416,7 @@
         <v>307</v>
       </c>
       <c r="B255" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C255" t="n">
         <v>0</v>
@@ -41440,10 +41440,10 @@
         <v>0.0045703374571644</v>
       </c>
       <c r="J255" t="n">
-        <v>42163.7517784315</v>
+        <v>42209.7383459007</v>
       </c>
       <c r="K255" t="n">
-        <v>28613.5463047015</v>
+        <v>28691.7962609847</v>
       </c>
       <c r="L255" t="n">
         <v>0</v>
@@ -41574,7 +41574,7 @@
         <v>308</v>
       </c>
       <c r="B256" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C256" t="n">
         <v>0</v>
@@ -41598,10 +41598,10 @@
         <v>0.00455315812106338</v>
       </c>
       <c r="J256" t="n">
-        <v>42556.8914406022</v>
+        <v>42603.3067921059</v>
       </c>
       <c r="K256" t="n">
-        <v>28896.9994261296</v>
+        <v>28976.02454653</v>
       </c>
       <c r="L256" t="n">
         <v>0</v>
@@ -41732,7 +41732,7 @@
         <v>309</v>
       </c>
       <c r="B257" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C257" t="n">
         <v>0</v>
@@ -41756,10 +41756,10 @@
         <v>0.00452892359824597</v>
       </c>
       <c r="J257" t="n">
-        <v>42953.34492368</v>
+        <v>43000.1926734898</v>
       </c>
       <c r="K257" t="n">
-        <v>29179.751674421</v>
+        <v>29259.5500422488</v>
       </c>
       <c r="L257" t="n">
         <v>0</v>
@@ -41890,7 +41890,7 @@
         <v>310</v>
       </c>
       <c r="B258" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C258" t="n">
         <v>0</v>
@@ -41914,10 +41914,10 @@
         <v>0.00451208594449426</v>
       </c>
       <c r="J258" t="n">
-        <v>43351.0034325423</v>
+        <v>43398.2848949388</v>
       </c>
       <c r="K258" t="n">
-        <v>29464.0057937197</v>
+        <v>29544.5815161672</v>
       </c>
       <c r="L258" t="n">
         <v>0</v>
@@ -42048,7 +42048,7 @@
         <v>311</v>
       </c>
       <c r="B259" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C259" t="n">
         <v>0</v>
@@ -42072,10 +42072,10 @@
         <v>0.00448825353819826</v>
       </c>
       <c r="J259" t="n">
-        <v>43753.9841386192</v>
+        <v>43801.7051183415</v>
       </c>
       <c r="K259" t="n">
-        <v>29750.7630313637</v>
+        <v>29832.1229537517</v>
       </c>
       <c r="L259" t="n">
         <v>0</v>
@@ -42206,7 +42206,7 @@
         <v>312</v>
       </c>
       <c r="B260" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C260" t="n">
         <v>0</v>
@@ -42230,10 +42230,10 @@
         <v>0.00446819912765406</v>
       </c>
       <c r="J260" t="n">
-        <v>44161.584110203</v>
+        <v>44209.7496453267</v>
       </c>
       <c r="K260" t="n">
-        <v>30040.1235120868</v>
+        <v>30122.2747535489</v>
       </c>
       <c r="L260" t="n">
         <v>0</v>

--- a/results/02-2026/beta/inputs-02-2026.xlsx
+++ b/results/02-2026/beta/inputs-02-2026.xlsx
@@ -36840,7 +36840,7 @@
         <v>0</v>
       </c>
       <c r="D226" t="n">
-        <v>-0.0285004322590822</v>
+        <v>-0.0206881991200681</v>
       </c>
       <c r="E226" t="n">
         <v>0.00825837924065231</v>
@@ -36867,7 +36867,7 @@
         <v>0.06</v>
       </c>
       <c r="M226" t="n">
-        <v>2074.88109070427</v>
+        <v>2081.49848380798</v>
       </c>
       <c r="N226" t="n">
         <v>412.463197887809</v>
@@ -37025,7 +37025,7 @@
         <v>0.06</v>
       </c>
       <c r="M227" t="n">
-        <v>2068.01554384286</v>
+        <v>2084.61104074122</v>
       </c>
       <c r="N227" t="n">
         <v>412.439192359044</v>
@@ -37183,7 +37183,7 @@
         <v>0.06</v>
       </c>
       <c r="M228" t="n">
-        <v>2084.18801581993</v>
+        <v>2092.91329424209</v>
       </c>
       <c r="N228" t="n">
         <v>416.245569392601</v>
@@ -37341,7 +37341,7 @@
         <v>0.06</v>
       </c>
       <c r="M229" t="n">
-        <v>2097.08359160202</v>
+        <v>2105.86285627122</v>
       </c>
       <c r="N229" t="n">
         <v>418.0795988</v>
@@ -37499,7 +37499,7 @@
         <v>0.06</v>
       </c>
       <c r="M230" t="n">
-        <v>2108.83815681017</v>
+        <v>2117.6666309813</v>
       </c>
       <c r="N230" t="n">
         <v>420.941553051321</v>
@@ -37657,7 +37657,7 @@
         <v>0.06</v>
       </c>
       <c r="M231" t="n">
-        <v>2119.75075118607</v>
+        <v>2128.62491001881</v>
       </c>
       <c r="N231" t="n">
         <v>423.831707301406</v>
@@ -37815,7 +37815,7 @@
         <v>0</v>
       </c>
       <c r="M232" t="n">
-        <v>2131.26227483347</v>
+        <v>2140.18462569501</v>
       </c>
       <c r="N232" t="n">
         <v>426.750339416305</v>
@@ -37973,7 +37973,7 @@
         <v>0</v>
       </c>
       <c r="M233" t="n">
-        <v>2137.26831123599</v>
+        <v>2146.21580586548</v>
       </c>
       <c r="N233" t="n">
         <v>429.69773</v>

--- a/results/02-2026/beta/inputs-02-2026.xlsx
+++ b/results/02-2026/beta/inputs-02-2026.xlsx
@@ -36867,7 +36867,7 @@
         <v>0.06</v>
       </c>
       <c r="M226" t="n">
-        <v>2081.49848380798</v>
+        <v>2044.88109070427</v>
       </c>
       <c r="N226" t="n">
         <v>412.463197887809</v>
@@ -37025,7 +37025,7 @@
         <v>0.06</v>
       </c>
       <c r="M227" t="n">
-        <v>2084.61104074122</v>
+        <v>2028.11481044988</v>
       </c>
       <c r="N227" t="n">
         <v>412.439192359044</v>
@@ -37183,7 +37183,7 @@
         <v>0.06</v>
       </c>
       <c r="M228" t="n">
-        <v>2092.91329424209</v>
+        <v>2033.97524730005</v>
       </c>
       <c r="N228" t="n">
         <v>416.245569392601</v>
@@ -37341,7 +37341,7 @@
         <v>0.06</v>
       </c>
       <c r="M229" t="n">
-        <v>2105.86285627122</v>
+        <v>2046.56013970963</v>
       </c>
       <c r="N229" t="n">
         <v>418.0795988</v>
@@ -37499,7 +37499,7 @@
         <v>0.06</v>
       </c>
       <c r="M230" t="n">
-        <v>2117.6666309813</v>
+        <v>2058.0315110517</v>
       </c>
       <c r="N230" t="n">
         <v>420.941553051321</v>
@@ -37657,7 +37657,7 @@
         <v>0.06</v>
       </c>
       <c r="M231" t="n">
-        <v>2128.62491001881</v>
+        <v>2068.68119652917</v>
       </c>
       <c r="N231" t="n">
         <v>423.831707301406</v>
@@ -37815,7 +37815,7 @@
         <v>0</v>
       </c>
       <c r="M232" t="n">
-        <v>2140.18462569501</v>
+        <v>2079.91538172734</v>
       </c>
       <c r="N232" t="n">
         <v>426.750339416305</v>
@@ -37973,7 +37973,7 @@
         <v>0</v>
       </c>
       <c r="M233" t="n">
-        <v>2146.21580586548</v>
+        <v>2085.77671922875</v>
       </c>
       <c r="N233" t="n">
         <v>429.69773</v>
